--- a/output/2026-08-28/enriched_analysis.xlsx
+++ b/output/2026-08-28/enriched_analysis.xlsx
@@ -640,13 +640,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>254.85</v>
+        <v>256.47</v>
       </c>
       <c r="J2" t="n">
         <v>158.6</v>
       </c>
       <c r="K2" t="n">
-        <v>60.7</v>
+        <v>61.7</v>
       </c>
       <c r="L2" t="n">
         <v>64.63</v>
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="Q2" t="n">
-        <v>2494</v>
+        <v>2508</v>
       </c>
       <c r="R2" t="n">
-        <v>8.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -696,13 +696,13 @@
         <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>221.41</v>
+        <v>223.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>163.15</v>
+        <v>163.77</v>
       </c>
       <c r="AC2" t="n">
-        <v>77.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -737,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>95.20999999999999</v>
+        <v>93.86</v>
       </c>
       <c r="J3" t="n">
         <v>55.78</v>
       </c>
       <c r="K3" t="n">
-        <v>70.7</v>
+        <v>68.3</v>
       </c>
       <c r="L3" t="n">
         <v>67.45999999999999</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.621</v>
+        <v>0.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>997</v>
+        <v>983</v>
       </c>
       <c r="R3" t="n">
-        <v>28.5</v>
+        <v>28.1</v>
       </c>
       <c r="S3" t="n">
         <v>19</v>
@@ -793,24 +793,24 @@
         <v>15.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>73.05</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>56.42</v>
+        <v>56.69</v>
       </c>
       <c r="AC3" t="n">
-        <v>88.5</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>MACPOWER CNC MACHINES LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -822,96 +822,96 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5502</v>
+        <v>2007.1</v>
       </c>
       <c r="J4" t="n">
-        <v>5187.29</v>
+        <v>920.51</v>
       </c>
       <c r="K4" t="n">
-        <v>6.1</v>
+        <v>118</v>
       </c>
       <c r="L4" t="n">
-        <v>67.16</v>
+        <v>73.16</v>
       </c>
       <c r="M4" t="n">
-        <v>6.71</v>
+        <v>0.44</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.039</v>
+        <v>0.022</v>
       </c>
       <c r="Q4" t="n">
-        <v>17101</v>
+        <v>2008</v>
       </c>
       <c r="R4" t="n">
-        <v>43.5</v>
+        <v>51.6</v>
       </c>
       <c r="S4" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="T4" t="n">
-        <v>145</v>
+        <v>15.42</v>
       </c>
       <c r="U4" t="n">
-        <v>264</v>
+        <v>47</v>
       </c>
       <c r="V4" t="n">
-        <v>27.38</v>
+        <v>9.58</v>
       </c>
       <c r="W4" t="n">
-        <v>25.5</v>
+        <v>29.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.64</v>
+        <v>0.01</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>16.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>5883.23</v>
+        <v>1512.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>4262.86</v>
+        <v>1109.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>54.7</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MACPOWER CNC MACHINES LIMITED</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -931,51 +931,51 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1868.8</v>
+        <v>238.75</v>
       </c>
       <c r="J5" t="n">
-        <v>920.51</v>
+        <v>217.8</v>
       </c>
       <c r="K5" t="n">
-        <v>103</v>
+        <v>9.6</v>
       </c>
       <c r="L5" t="n">
-        <v>73.16</v>
+        <v>71.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0.44</v>
+        <v>0.82</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.024</v>
+        <v>0.078</v>
       </c>
       <c r="Q5" t="n">
-        <v>1870</v>
+        <v>1047</v>
       </c>
       <c r="R5" t="n">
-        <v>48.1</v>
+        <v>14.1</v>
       </c>
       <c r="S5" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="T5" t="n">
-        <v>15.42</v>
+        <v>40</v>
       </c>
       <c r="U5" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="V5" t="n">
-        <v>9.58</v>
+        <v>8.23</v>
       </c>
       <c r="W5" t="n">
-        <v>29.1</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
         <v>0.01</v>
@@ -984,31 +984,31 @@
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.19</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>1493.12</v>
+        <v>213.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>1103.82</v>
+        <v>180.81</v>
       </c>
       <c r="AC5" t="n">
-        <v>108</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1016,96 +1016,96 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>824</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>752.23</v>
+        <v>70.27</v>
       </c>
       <c r="K6" t="n">
-        <v>9.5</v>
+        <v>2.1</v>
       </c>
       <c r="L6" t="n">
-        <v>69.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>15.13</v>
+        <v>0.7</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.093</v>
+        <v>0.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>16197</v>
+        <v>212</v>
       </c>
       <c r="R6" t="n">
-        <v>20.5</v>
+        <v>8.99</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
-        <v>346</v>
+        <v>27.97</v>
       </c>
       <c r="U6" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="V6" t="n">
-        <v>10.02</v>
+        <v>2.73</v>
       </c>
       <c r="W6" t="n">
-        <v>12.3</v>
+        <v>13.7</v>
       </c>
       <c r="X6" t="n">
-        <v>0.21</v>
+        <v>1.86</v>
       </c>
       <c r="Y6" t="b">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>815.4299999999999</v>
+        <v>55.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>792.85</v>
+        <v>51.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THANGAMAIYL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1113,92 +1113,92 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>71.66</v>
+        <v>5440.5</v>
       </c>
       <c r="J7" t="n">
-        <v>70.27</v>
+        <v>5187.29</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>72.56999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>6.71</v>
       </c>
       <c r="N7" t="n">
         <v>5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.332</v>
+        <v>0.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>211</v>
+        <v>16911</v>
       </c>
       <c r="R7" t="n">
-        <v>8.970000000000001</v>
+        <v>43.1</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="T7" t="n">
-        <v>27.97</v>
+        <v>145</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="V7" t="n">
-        <v>2.73</v>
+        <v>27.38</v>
       </c>
       <c r="W7" t="n">
-        <v>13.7</v>
+        <v>25.5</v>
       </c>
       <c r="X7" t="n">
-        <v>1.86</v>
+        <v>0.64</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.140000000000001</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>55.1</v>
+        <v>5883.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>51.23</v>
+        <v>4274.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>49.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1222,181 +1222,179 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>227.39</v>
+        <v>813.45</v>
       </c>
       <c r="J8" t="n">
-        <v>217.8</v>
+        <v>752.23</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="L8" t="n">
-        <v>71.75</v>
+        <v>69.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.82</v>
+        <v>15.13</v>
       </c>
       <c r="N8" t="n">
         <v>5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.083</v>
+        <v>0.095</v>
       </c>
       <c r="Q8" t="n">
-        <v>992</v>
+        <v>15999</v>
       </c>
       <c r="R8" t="n">
-        <v>13.4</v>
+        <v>20.3</v>
       </c>
       <c r="S8" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>40</v>
+        <v>346</v>
       </c>
       <c r="U8" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="V8" t="n">
-        <v>8.23</v>
+        <v>10.02</v>
       </c>
       <c r="W8" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>213.34</v>
+        <v>816.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>180.65</v>
+        <v>792.34</v>
       </c>
       <c r="AC8" t="n">
-        <v>44.7</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Strong Buy Setup</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>362.75</v>
+        <v>542.25</v>
       </c>
       <c r="J9" t="n">
-        <v>335.41</v>
+        <v>390.61</v>
       </c>
       <c r="K9" t="n">
-        <v>8.199999999999999</v>
+        <v>38.8</v>
       </c>
       <c r="L9" t="n">
-        <v>68.48</v>
+        <v>63.09</v>
       </c>
       <c r="M9" t="n">
-        <v>0.41</v>
+        <v>8.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.007</v>
+        <v>0.467</v>
       </c>
       <c r="Q9" t="n">
-        <v>5946</v>
+        <v>1719</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>20.4</v>
       </c>
       <c r="S9" t="n">
-        <v>43</v>
+        <v>581</v>
       </c>
       <c r="T9" t="n">
-        <v>223</v>
+        <v>34</v>
       </c>
       <c r="U9" t="n">
-        <v>175</v>
+        <v>881</v>
       </c>
       <c r="V9" t="n">
-        <v>6.97</v>
+        <v>8.58</v>
       </c>
       <c r="W9" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0.33</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>362.55</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>332.99</v>
-      </c>
+        <v>463.54</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>11.3</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,79 +1402,79 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>542.9</v>
+        <v>192.36</v>
       </c>
       <c r="J10" t="n">
-        <v>390.61</v>
+        <v>164.1</v>
       </c>
       <c r="K10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4065</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>39</v>
       </c>
-      <c r="L10" t="n">
-        <v>63.09</v>
-      </c>
-      <c r="M10" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1721</v>
-      </c>
-      <c r="R10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>581</v>
-      </c>
       <c r="T10" t="n">
-        <v>34</v>
+        <v>258</v>
       </c>
       <c r="U10" t="n">
-        <v>881</v>
+        <v>30</v>
       </c>
       <c r="V10" t="n">
-        <v>8.58</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>22</v>
+        <v>6.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0.33</v>
+        <v>10.11</v>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="AA10" t="n">
-        <v>460.42</v>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+        <v>177.15</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>178.89</v>
+      </c>
       <c r="AC10" t="n">
-        <v>31.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="11">
@@ -1511,13 +1509,13 @@
         <v>-3</v>
       </c>
       <c r="I11" t="n">
-        <v>269.84</v>
+        <v>267.49</v>
       </c>
       <c r="J11" t="n">
         <v>243.52</v>
       </c>
       <c r="K11" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>67.65000000000001</v>
@@ -1534,13 +1532,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="Q11" t="n">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="R11" t="n">
-        <v>60.6</v>
+        <v>60.1</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1567,24 +1565,24 @@
         <v>16.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>244.22</v>
+        <v>245.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>177.4</v>
+        <v>177.97</v>
       </c>
       <c r="AC11" t="n">
-        <v>74.2</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1596,10 +1594,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -1608,78 +1606,80 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>191.06</v>
+        <v>366.7</v>
       </c>
       <c r="J12" t="n">
-        <v>164.1</v>
+        <v>338.1</v>
       </c>
       <c r="K12" t="n">
-        <v>16.4</v>
+        <v>8.5</v>
       </c>
       <c r="L12" t="n">
-        <v>60.6</v>
+        <v>66.73</v>
       </c>
       <c r="M12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.006</v>
+        <v>0.079</v>
       </c>
       <c r="Q12" t="n">
-        <v>4050</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
+        <v>433</v>
+      </c>
+      <c r="R12" t="n">
+        <v>12.8</v>
+      </c>
       <c r="S12" t="n">
-        <v>39</v>
+        <v>-8</v>
       </c>
       <c r="T12" t="n">
-        <v>258</v>
+        <v>24</v>
       </c>
       <c r="U12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.13</v>
+        <v>14.36</v>
       </c>
       <c r="W12" t="n">
-        <v>6.38</v>
+        <v>9.94</v>
       </c>
       <c r="X12" t="n">
-        <v>10.11</v>
+        <v>0.23</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>176.7</v>
+        <v>316.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>178.96</v>
+        <v>259</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.9</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1703,84 +1703,84 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>365.9</v>
+        <v>354.85</v>
       </c>
       <c r="J13" t="n">
-        <v>338.1</v>
+        <v>335.41</v>
       </c>
       <c r="K13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="L13" t="n">
-        <v>66.73</v>
+        <v>68.48</v>
       </c>
       <c r="M13" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.079</v>
+        <v>0.007</v>
       </c>
       <c r="Q13" t="n">
-        <v>431</v>
+        <v>5814</v>
       </c>
       <c r="R13" t="n">
-        <v>12.7</v>
+        <v>9.83</v>
       </c>
       <c r="S13" t="n">
-        <v>-8</v>
+        <v>43</v>
       </c>
       <c r="T13" t="n">
-        <v>24</v>
+        <v>223</v>
       </c>
       <c r="U13" t="n">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="V13" t="n">
-        <v>14.36</v>
+        <v>6.97</v>
       </c>
       <c r="W13" t="n">
-        <v>9.94</v>
+        <v>21.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0.23</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>314.35</v>
+        <v>362.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>258.53</v>
+        <v>333.13</v>
       </c>
       <c r="AC13" t="n">
-        <v>66.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1797,72 +1797,72 @@
         <v>30</v>
       </c>
       <c r="H14" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I14" t="n">
-        <v>622.6</v>
+        <v>331.05</v>
       </c>
       <c r="J14" t="n">
-        <v>567.47</v>
+        <v>311.69</v>
       </c>
       <c r="K14" t="n">
-        <v>9.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
-        <v>64.68000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="M14" t="n">
-        <v>5.47</v>
+        <v>1.41</v>
       </c>
       <c r="N14" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.476</v>
+        <v>0.446</v>
       </c>
       <c r="Q14" t="n">
-        <v>1149</v>
+        <v>316</v>
       </c>
       <c r="R14" t="n">
-        <v>58.5</v>
+        <v>146</v>
       </c>
       <c r="S14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.11</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>23</v>
+        <v>264</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.58</v>
+        <v>2.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y14" t="b">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-110</v>
+        <v>6.06</v>
       </c>
       <c r="AA14" t="n">
-        <v>571.83</v>
+        <v>289.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>503.54</v>
+        <v>276.49</v>
       </c>
       <c r="AC14" t="n">
-        <v>28.1</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="15">
@@ -1953,28 +1953,28 @@
         <v>3.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>104.5</v>
+        <v>105.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>68.84999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>133.8</v>
+        <v>138.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,85 +1985,89 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="I16" t="n">
-        <v>20.1</v>
+        <v>636.9</v>
       </c>
       <c r="J16" t="n">
-        <v>21.01</v>
+        <v>567.47</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.3</v>
+        <v>12.2</v>
       </c>
       <c r="L16" t="n">
-        <v>70.87</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5</v>
+        <v>5.47</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.131</v>
+        <v>0.462</v>
       </c>
       <c r="Q16" t="n">
-        <v>382</v>
+        <v>1184</v>
       </c>
       <c r="R16" t="n">
-        <v>6.17</v>
+        <v>60.3</v>
       </c>
       <c r="S16" t="n">
-        <v>118</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.11</v>
+      </c>
       <c r="U16" t="n">
-        <v>391</v>
+        <v>23</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>18.5</v>
+        <v>1.58</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="b">
         <v>0</v>
       </c>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>-110</v>
+      </c>
       <c r="AA16" t="n">
-        <v>17.79</v>
+        <v>572.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>15.06</v>
+        <v>504.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2078,93 +2082,89 @@
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>79.92</v>
+        <v>19.86</v>
       </c>
       <c r="J17" t="n">
-        <v>74.92</v>
+        <v>21.01</v>
       </c>
       <c r="K17" t="n">
-        <v>6.7</v>
+        <v>-5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>62.78</v>
+        <v>70.87</v>
       </c>
       <c r="M17" t="n">
-        <v>1.48</v>
+        <v>0.5</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.361</v>
+        <v>0.132</v>
       </c>
       <c r="Q17" t="n">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="R17" t="n">
-        <v>38</v>
+        <v>6.1</v>
       </c>
       <c r="S17" t="n">
-        <v>21</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8.390000000000001</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>-19</v>
+        <v>391</v>
       </c>
       <c r="V17" t="n">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>8.73</v>
+        <v>18.5</v>
       </c>
       <c r="X17" t="n">
-        <v>0.28</v>
+        <v>0.01</v>
       </c>
       <c r="Y17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>41.64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
-        <v>75.69</v>
+        <v>17.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>78.38</v>
+        <v>15.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.1</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
         <v>25</v>
@@ -2184,69 +2184,69 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>102.77</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>89.34</v>
+        <v>74.92</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>70.88</v>
+        <v>62.78</v>
       </c>
       <c r="M18" t="n">
-        <v>6.25</v>
+        <v>1.48</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.237</v>
+        <v>0.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>2639</v>
+        <v>423</v>
       </c>
       <c r="R18" t="n">
-        <v>21.6</v>
+        <v>39.3</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="T18" t="n">
-        <v>14</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-14</v>
+        <v>-19</v>
       </c>
       <c r="V18" t="n">
-        <v>0.57</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>16.9</v>
+        <v>8.73</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01</v>
+        <v>0.28</v>
       </c>
       <c r="Y18" t="b">
         <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>30</v>
+        <v>41.64</v>
       </c>
       <c r="AA18" t="n">
-        <v>90.15000000000001</v>
+        <v>75.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>92</v>
+        <v>78.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="19">
@@ -2281,13 +2281,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>133.81</v>
+        <v>139.39</v>
       </c>
       <c r="J19" t="n">
         <v>100.9</v>
       </c>
       <c r="K19" t="n">
-        <v>32.6</v>
+        <v>38.1</v>
       </c>
       <c r="L19" t="n">
         <v>69.56</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.209</v>
+        <v>0.203</v>
       </c>
       <c r="Q19" t="n">
-        <v>1437</v>
+        <v>1482</v>
       </c>
       <c r="R19" t="n">
-        <v>50.1</v>
+        <v>51.7</v>
       </c>
       <c r="S19" t="n">
         <v>7</v>
@@ -2337,28 +2337,28 @@
         <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>120.43</v>
+        <v>121.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>115.4</v>
+        <v>115.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>27.1</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2369,93 +2369,93 @@
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
         <v>25</v>
       </c>
       <c r="H20" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>319.9</v>
+        <v>100.04</v>
       </c>
       <c r="J20" t="n">
-        <v>311.69</v>
+        <v>89.34</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="L20" t="n">
-        <v>63.24</v>
+        <v>70.88</v>
       </c>
       <c r="M20" t="n">
-        <v>1.41</v>
+        <v>6.25</v>
       </c>
       <c r="N20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.462</v>
+        <v>0.243</v>
       </c>
       <c r="Q20" t="n">
-        <v>305</v>
+        <v>2573</v>
       </c>
       <c r="R20" t="n">
-        <v>141</v>
+        <v>21.1</v>
       </c>
       <c r="S20" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>14</v>
       </c>
       <c r="U20" t="n">
-        <v>264</v>
+        <v>-14</v>
       </c>
       <c r="V20" t="n">
-        <v>2.55</v>
+        <v>0.57</v>
       </c>
       <c r="W20" t="n">
-        <v>2.07</v>
+        <v>16.9</v>
       </c>
       <c r="X20" t="n">
         <v>0.01</v>
       </c>
       <c r="Y20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.06</v>
+        <v>30</v>
       </c>
       <c r="AA20" t="n">
-        <v>288.08</v>
+        <v>90.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>276.19</v>
+        <v>92</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OBCL LIMITED (FORMERLY KNOWN AS ORISSA BENGAL CARRIER LIMITED)</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
         <v>25</v>
@@ -2475,82 +2475,84 @@
         <v>-2</v>
       </c>
       <c r="I21" t="n">
-        <v>56.16</v>
+        <v>213</v>
       </c>
       <c r="J21" t="n">
-        <v>53.44</v>
+        <v>209.98</v>
       </c>
       <c r="K21" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="L21" t="n">
-        <v>67.23</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>1.88</v>
+        <v>0.26</v>
       </c>
       <c r="N21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.593</v>
+        <v>0.131</v>
       </c>
       <c r="Q21" t="n">
-        <v>118</v>
-      </c>
-      <c r="R21" t="inlineStr"/>
+        <v>199</v>
+      </c>
+      <c r="R21" t="n">
+        <v>24.8</v>
+      </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>2.47</v>
+        <v>0.03</v>
       </c>
       <c r="U21" t="n">
-        <v>-3779</v>
+        <v>16</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.26</v>
+        <v>7.91</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>54.3</v>
+        <v>206.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>55.13</v>
+        <v>194.89</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2558,96 +2560,96 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" t="n">
         <v>10</v>
       </c>
-      <c r="G22" t="n">
-        <v>25</v>
-      </c>
       <c r="H22" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>212.68</v>
+        <v>1316.1</v>
       </c>
       <c r="J22" t="n">
-        <v>209.98</v>
+        <v>1104.34</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3</v>
+        <v>19.2</v>
       </c>
       <c r="L22" t="n">
-        <v>67.04000000000001</v>
+        <v>60.82</v>
       </c>
       <c r="M22" t="n">
-        <v>0.26</v>
+        <v>5.22</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.131</v>
+        <v>0.001</v>
       </c>
       <c r="Q22" t="n">
-        <v>199</v>
+        <v>357090</v>
       </c>
       <c r="R22" t="n">
-        <v>24.7</v>
+        <v>19.6</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>0.03</v>
+        <v>4158</v>
       </c>
       <c r="U22" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="V22" t="n">
-        <v>0.03</v>
+        <v>25.89</v>
       </c>
       <c r="W22" t="n">
-        <v>7.91</v>
+        <v>53.4</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="Y22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.16</v>
+        <v>29</v>
       </c>
       <c r="AA22" t="n">
-        <v>206.4</v>
+        <v>1246.07</v>
       </c>
       <c r="AB22" t="n">
-        <v>194.82</v>
+        <v>1396.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>14.1</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2655,92 +2657,92 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1282</v>
+        <v>122.81</v>
       </c>
       <c r="J23" t="n">
-        <v>1104.34</v>
+        <v>105.19</v>
       </c>
       <c r="K23" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="L23" t="n">
-        <v>60.82</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>5.22</v>
+        <v>2.63</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.002</v>
+        <v>0.053</v>
       </c>
       <c r="Q23" t="n">
-        <v>347892</v>
+        <v>4965</v>
       </c>
       <c r="R23" t="n">
-        <v>19.1</v>
+        <v>32.4</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>-25</v>
       </c>
       <c r="T23" t="n">
-        <v>4158</v>
+        <v>71</v>
       </c>
       <c r="U23" t="n">
-        <v>44</v>
+        <v>-11</v>
       </c>
       <c r="V23" t="n">
-        <v>25.89</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>53.4</v>
+        <v>10.7</v>
       </c>
       <c r="X23" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="AA23" t="n">
-        <v>1242.98</v>
+        <v>105.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1397.31</v>
+        <v>112.38</v>
       </c>
       <c r="AC23" t="n">
-        <v>-10.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2752,189 +2754,187 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
         <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I24" t="n">
-        <v>115.46</v>
+        <v>13.9</v>
       </c>
       <c r="J24" t="n">
-        <v>105.19</v>
+        <v>12.31</v>
       </c>
       <c r="K24" t="n">
-        <v>9.800000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="L24" t="n">
-        <v>67.15000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="M24" t="n">
-        <v>2.63</v>
+        <v>1.35</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.056</v>
+        <v>0.345</v>
       </c>
       <c r="Q24" t="n">
-        <v>4661</v>
+        <v>391</v>
       </c>
       <c r="R24" t="n">
-        <v>30.4</v>
+        <v>1260</v>
       </c>
       <c r="S24" t="n">
-        <v>-25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>71</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>-11</v>
+        <v>-98</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>0.01</v>
       </c>
       <c r="W24" t="n">
-        <v>10.7</v>
+        <v>2.46</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
       </c>
-      <c r="Z24" t="n">
-        <v>69</v>
-      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
-        <v>105</v>
+        <v>11.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>112.45</v>
+        <v>13.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.8</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Buy on Breakout</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="I25" t="n">
-        <v>13.68</v>
+        <v>55.4</v>
       </c>
       <c r="J25" t="n">
-        <v>12.28</v>
+        <v>53.44</v>
       </c>
       <c r="K25" t="n">
-        <v>11.4</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>69.12</v>
+        <v>67.23</v>
       </c>
       <c r="M25" t="n">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.345</v>
+        <v>1.621</v>
       </c>
       <c r="Q25" t="n">
-        <v>386</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1245</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T25" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.47</v>
+      </c>
       <c r="U25" t="n">
-        <v>-98</v>
+        <v>-3779</v>
       </c>
       <c r="V25" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="W25" t="n">
-        <v>2.46</v>
+        <v>-1.26</v>
       </c>
       <c r="X25" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
       </c>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>3</v>
+      </c>
       <c r="AA25" t="n">
-        <v>11</v>
+        <v>54.27</v>
       </c>
       <c r="AB25" t="n">
-        <v>13.57</v>
+        <v>55.13</v>
       </c>
       <c r="AC25" t="n">
-        <v>-8.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2942,96 +2942,96 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>110.06</v>
+        <v>322</v>
       </c>
       <c r="J26" t="n">
-        <v>109.31</v>
+        <v>297.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>72.34</v>
+        <v>67.69</v>
       </c>
       <c r="M26" t="n">
-        <v>48.4</v>
+        <v>2.97</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.274</v>
       </c>
       <c r="Q26" t="n">
-        <v>5177</v>
+        <v>1082</v>
       </c>
       <c r="R26" t="n">
-        <v>41.5</v>
+        <v>19.2</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T26" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="U26" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V26" t="n">
-        <v>1.25</v>
+        <v>4.07</v>
       </c>
       <c r="W26" t="n">
-        <v>9.710000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0.06</v>
+        <v>0.47</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>105.71</v>
+        <v>333.76</v>
       </c>
       <c r="AB26" t="n">
-        <v>114.47</v>
+        <v>349.79</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.7</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3039,96 +3039,96 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>320.9</v>
+        <v>178.22</v>
       </c>
       <c r="J27" t="n">
-        <v>297.3</v>
+        <v>180.98</v>
       </c>
       <c r="K27" t="n">
-        <v>7.9</v>
+        <v>-1.5</v>
       </c>
       <c r="L27" t="n">
-        <v>67.69</v>
+        <v>74.59</v>
       </c>
       <c r="M27" t="n">
-        <v>2.97</v>
+        <v>0.25</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.275</v>
+        <v>0.011</v>
       </c>
       <c r="Q27" t="n">
-        <v>1080</v>
+        <v>2258</v>
       </c>
       <c r="R27" t="n">
-        <v>19.2</v>
+        <v>51.8</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="U27" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="V27" t="n">
-        <v>4.07</v>
+        <v>0.8</v>
       </c>
       <c r="W27" t="n">
-        <v>11.5</v>
+        <v>30.3</v>
       </c>
       <c r="X27" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA27" t="n">
-        <v>333.67</v>
+        <v>192.38</v>
       </c>
       <c r="AB27" t="n">
-        <v>350.41</v>
+        <v>557.0599999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9</v>
+        <v>-87.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3136,63 +3136,63 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H28" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="I28" t="n">
-        <v>43.09</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>43.04</v>
+        <v>29.14</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1</v>
+        <v>-7.3</v>
       </c>
       <c r="L28" t="n">
-        <v>71.79000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="M28" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="N28" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.239</v>
+        <v>1.288</v>
       </c>
       <c r="Q28" t="n">
-        <v>427</v>
+        <v>104</v>
       </c>
       <c r="R28" t="n">
-        <v>106</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>246</v>
+        <v>-1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.91</v>
+        <v>0.4</v>
       </c>
       <c r="U28" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="V28" t="n">
-        <v>0.14</v>
+        <v>0.59</v>
       </c>
       <c r="W28" t="n">
-        <v>2.16</v>
+        <v>-0.18</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -3201,31 +3201,31 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.21</v>
+        <v>21.51</v>
       </c>
       <c r="AA28" t="n">
-        <v>40.73</v>
+        <v>27.41</v>
       </c>
       <c r="AB28" t="n">
-        <v>39.65</v>
+        <v>24.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3233,96 +3233,96 @@
         </is>
       </c>
       <c r="E29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F29" t="n">
         <v>25</v>
       </c>
-      <c r="F29" t="n">
-        <v>10</v>
-      </c>
       <c r="G29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>26.81</v>
+        <v>174.15</v>
       </c>
       <c r="J29" t="n">
-        <v>29.14</v>
+        <v>201.21</v>
       </c>
       <c r="K29" t="n">
-        <v>-8</v>
+        <v>-13.4</v>
       </c>
       <c r="L29" t="n">
-        <v>69.03</v>
+        <v>64.08</v>
       </c>
       <c r="M29" t="n">
-        <v>1.34</v>
+        <v>8.07</v>
       </c>
       <c r="N29" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.288</v>
+        <v>1.146</v>
       </c>
       <c r="Q29" t="n">
-        <v>104</v>
+        <v>704</v>
       </c>
       <c r="R29" t="n">
-        <v>74.7</v>
+        <v>15.5</v>
       </c>
       <c r="S29" t="n">
         <v>-1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4</v>
+        <v>21</v>
       </c>
       <c r="U29" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="V29" t="n">
-        <v>0.59</v>
+        <v>3.1</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.18</v>
+        <v>19.4</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.51</v>
+        <v>11</v>
       </c>
       <c r="AA29" t="n">
-        <v>27.47</v>
+        <v>177.46</v>
       </c>
       <c r="AB29" t="n">
-        <v>24.59</v>
+        <v>200.72</v>
       </c>
       <c r="AC29" t="n">
-        <v>25.1</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3330,96 +3330,94 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>178.58</v>
+        <v>744.75</v>
       </c>
       <c r="J30" t="n">
-        <v>180.98</v>
+        <v>717.77</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.3</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>74.59</v>
+        <v>61.71</v>
       </c>
       <c r="M30" t="n">
-        <v>0.25</v>
+        <v>1.61</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.011</v>
+        <v>0.697</v>
       </c>
       <c r="Q30" t="n">
-        <v>2265</v>
-      </c>
-      <c r="R30" t="n">
-        <v>52</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T30" t="n">
-        <v>17</v>
+        <v>11.91</v>
       </c>
       <c r="U30" t="n">
-        <v>83</v>
+        <v>-184</v>
       </c>
       <c r="V30" t="n">
-        <v>0.8</v>
+        <v>31.98</v>
       </c>
       <c r="W30" t="n">
-        <v>30.3</v>
+        <v>0.27</v>
       </c>
       <c r="X30" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>23</v>
+        <v>57.93</v>
       </c>
       <c r="AA30" t="n">
-        <v>192.53</v>
+        <v>731.34</v>
       </c>
       <c r="AB30" t="n">
-        <v>560.12</v>
+        <v>760.58</v>
       </c>
       <c r="AC30" t="n">
-        <v>-87.2</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3430,89 +3428,87 @@
         <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>163.49</v>
+        <v>175.31</v>
       </c>
       <c r="J31" t="n">
-        <v>204.13</v>
+        <v>182.69</v>
       </c>
       <c r="K31" t="n">
-        <v>-19.9</v>
+        <v>-4</v>
       </c>
       <c r="L31" t="n">
-        <v>64.08</v>
+        <v>69.05</v>
       </c>
       <c r="M31" t="n">
-        <v>7.57</v>
+        <v>0.74</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.145</v>
+        <v>0.123</v>
       </c>
       <c r="Q31" t="n">
-        <v>661</v>
+        <v>603</v>
       </c>
       <c r="R31" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="S31" t="n">
-        <v>-1</v>
+        <v>61</v>
       </c>
       <c r="T31" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="U31" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="V31" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="W31" t="n">
-        <v>19.4</v>
+        <v>42.7</v>
       </c>
       <c r="X31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="Y31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA31" t="n">
-        <v>177.94</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>201.16</v>
-      </c>
+        <v>171.77</v>
+      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>-10.3</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3524,10 +3520,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F32" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
         <v>5</v>
@@ -3536,78 +3532,80 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>172.27</v>
+        <v>108.43</v>
       </c>
       <c r="J32" t="n">
-        <v>182.69</v>
+        <v>109.31</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.7</v>
+        <v>-0.8</v>
       </c>
       <c r="L32" t="n">
-        <v>69.05</v>
+        <v>72.34</v>
       </c>
       <c r="M32" t="n">
-        <v>0.74</v>
+        <v>48.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.125</v>
+        <v>0.949</v>
       </c>
       <c r="Q32" t="n">
-        <v>590</v>
+        <v>5101</v>
       </c>
       <c r="R32" t="n">
-        <v>14</v>
+        <v>40.9</v>
       </c>
       <c r="S32" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="U32" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="V32" t="n">
-        <v>3.07</v>
+        <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>42.7</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="X32" t="n">
-        <v>0.35</v>
+        <v>0.06</v>
       </c>
       <c r="Y32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="n">
-        <v>171.83</v>
-      </c>
-      <c r="AB32" t="inlineStr"/>
+        <v>105.55</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>114.25</v>
+      </c>
       <c r="AC32" t="n">
-        <v>-10.9</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3619,94 +3617,96 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>751.85</v>
+        <v>509.7</v>
       </c>
       <c r="J33" t="n">
-        <v>717.77</v>
+        <v>545.03</v>
       </c>
       <c r="K33" t="n">
-        <v>4.7</v>
+        <v>-6.5</v>
       </c>
       <c r="L33" t="n">
-        <v>61.71</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="Q33" t="n">
-        <v>233</v>
-      </c>
-      <c r="R33" t="inlineStr"/>
+        <v>3222</v>
+      </c>
+      <c r="R33" t="n">
+        <v>21.8</v>
+      </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T33" t="n">
-        <v>11.91</v>
+        <v>97</v>
       </c>
       <c r="U33" t="n">
-        <v>-184</v>
+        <v>53</v>
       </c>
       <c r="V33" t="n">
-        <v>31.98</v>
+        <v>3.73</v>
       </c>
       <c r="W33" t="n">
-        <v>0.27</v>
+        <v>19.8</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>57.93</v>
+        <v>40</v>
       </c>
       <c r="AA33" t="n">
-        <v>731.62</v>
+        <v>530.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>760.35</v>
+        <v>562.98</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3714,81 +3714,81 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="I34" t="n">
-        <v>517.05</v>
+        <v>42.46</v>
       </c>
       <c r="J34" t="n">
-        <v>545.03</v>
+        <v>43.04</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.1</v>
+        <v>-1.3</v>
       </c>
       <c r="L34" t="n">
-        <v>69.90000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.033</v>
+        <v>0.243</v>
       </c>
       <c r="Q34" t="n">
-        <v>3261</v>
+        <v>420</v>
       </c>
       <c r="R34" t="n">
-        <v>22.1</v>
+        <v>104</v>
       </c>
       <c r="S34" t="n">
-        <v>17</v>
+        <v>246</v>
       </c>
       <c r="T34" t="n">
-        <v>97</v>
+        <v>0.91</v>
       </c>
       <c r="U34" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="V34" t="n">
-        <v>3.73</v>
+        <v>0.14</v>
       </c>
       <c r="W34" t="n">
-        <v>19.8</v>
+        <v>2.16</v>
       </c>
       <c r="X34" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>40</v>
+        <v>4.21</v>
       </c>
       <c r="AA34" t="n">
-        <v>531.78</v>
+        <v>40.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>563.13</v>
+        <v>39.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>-1.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="35">
@@ -3823,13 +3823,13 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>116.98</v>
+        <v>117.41</v>
       </c>
       <c r="J35" t="n">
         <v>114.86</v>
       </c>
       <c r="K35" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="L35" t="n">
         <v>69.73999999999999</v>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.32</v>
+        <v>0.319</v>
       </c>
       <c r="Q35" t="n">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="R35" t="n">
         <v>19.8</v>
@@ -3879,28 +3879,28 @@
         <v>38</v>
       </c>
       <c r="AA35" t="n">
-        <v>126.66</v>
+        <v>126.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>332.33</v>
+        <v>327.83</v>
       </c>
       <c r="AC35" t="n">
-        <v>-15.7</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3908,94 +3908,96 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>729.3</v>
+        <v>268.7</v>
       </c>
       <c r="J36" t="n">
-        <v>815.16</v>
+        <v>269.7</v>
       </c>
       <c r="K36" t="n">
-        <v>-10.5</v>
+        <v>-0.4</v>
       </c>
       <c r="L36" t="n">
-        <v>73.2</v>
+        <v>73.09</v>
       </c>
       <c r="M36" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.168</v>
+        <v>0.097</v>
       </c>
       <c r="Q36" t="n">
-        <v>738</v>
+        <v>1522</v>
       </c>
       <c r="R36" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="S36" t="n">
-        <v>185</v>
+        <v>6</v>
       </c>
       <c r="T36" t="n">
-        <v>11.55</v>
+        <v>46</v>
       </c>
       <c r="U36" t="n">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="V36" t="n">
-        <v>6.84</v>
+        <v>4.31</v>
       </c>
       <c r="W36" t="n">
-        <v>50.7</v>
+        <v>13.6</v>
       </c>
       <c r="X36" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="Y36" t="b">
         <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>16.07</v>
+        <v>12</v>
       </c>
       <c r="AA36" t="n">
-        <v>751.4</v>
-      </c>
-      <c r="AB36" t="inlineStr"/>
+        <v>267.86</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>294.37</v>
+      </c>
       <c r="AC36" t="n">
-        <v>-19.8</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4003,280 +4005,288 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>433.85</v>
+        <v>728.4</v>
       </c>
       <c r="J37" t="n">
-        <v>474.82</v>
+        <v>815.16</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.6</v>
+        <v>-10.6</v>
       </c>
       <c r="L37" t="n">
-        <v>70.55</v>
+        <v>73.2</v>
       </c>
       <c r="M37" t="n">
-        <v>10.22</v>
+        <v>1.24</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.275</v>
+        <v>0.168</v>
       </c>
       <c r="Q37" t="n">
-        <v>3720</v>
+        <v>737</v>
       </c>
       <c r="R37" t="n">
-        <v>26</v>
+        <v>13.4</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="T37" t="n">
-        <v>127</v>
+        <v>11.55</v>
       </c>
       <c r="U37" t="n">
-        <v>-14</v>
+        <v>204</v>
       </c>
       <c r="V37" t="n">
-        <v>6.41</v>
+        <v>6.84</v>
       </c>
       <c r="W37" t="n">
-        <v>9.890000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="n">
-        <v>21</v>
+        <v>16.07</v>
       </c>
       <c r="AA37" t="n">
-        <v>451.75</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>434.25</v>
-      </c>
+        <v>750.1</v>
+      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>6</v>
+        <v>-19.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>69.16</v>
+        <v>434.15</v>
       </c>
       <c r="J38" t="n">
-        <v>64.04000000000001</v>
+        <v>474.82</v>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>-8.6</v>
       </c>
       <c r="L38" t="n">
-        <v>64.29000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="M38" t="n">
-        <v>0.31</v>
+        <v>10.22</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.036</v>
+        <v>0.274</v>
       </c>
       <c r="Q38" t="n">
-        <v>850</v>
+        <v>3727</v>
       </c>
       <c r="R38" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
+        <v>26.1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2</v>
+      </c>
       <c r="T38" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
+        <v>127</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-14</v>
+      </c>
       <c r="V38" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W38" t="inlineStr"/>
+        <v>6.41</v>
+      </c>
+      <c r="W38" t="n">
+        <v>9.890000000000001</v>
+      </c>
       <c r="X38" t="n">
-        <v>0.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>12.14</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="n">
-        <v>65.86</v>
-      </c>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
+        <v>450.65</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>434.35</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>EUROPRATIK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>Euro Pratik Sales Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>17</v>
       </c>
       <c r="F39" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>56.95</v>
+        <v>257.45</v>
       </c>
       <c r="J39" t="n">
-        <v>60.15</v>
+        <v>257.65</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.3</v>
+        <v>-0.1</v>
       </c>
       <c r="L39" t="n">
-        <v>73.01000000000001</v>
+        <v>70.09</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9</v>
+        <v>1.64</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.182</v>
+        <v>0.062</v>
       </c>
       <c r="Q39" t="n">
-        <v>494</v>
+        <v>2633</v>
       </c>
       <c r="R39" t="n">
-        <v>12.3</v>
+        <v>45.8</v>
       </c>
       <c r="S39" t="n">
-        <v>19</v>
+        <v>-3</v>
       </c>
       <c r="T39" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="U39" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="V39" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>12</v>
+        <v>29.6</v>
       </c>
       <c r="X39" t="n">
-        <v>0.58</v>
+        <v>0.03</v>
       </c>
       <c r="Y39" t="b">
         <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.4</v>
+        <v>24</v>
       </c>
       <c r="AA39" t="n">
-        <v>57.94</v>
+        <v>294.37</v>
       </c>
       <c r="AB39" t="n">
-        <v>59.37</v>
+        <v>277.85</v>
       </c>
       <c r="AC39" t="n">
-        <v>-3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4284,96 +4294,96 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>265.25</v>
+        <v>175.95</v>
       </c>
       <c r="J40" t="n">
-        <v>269.7</v>
+        <v>173.91</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.6</v>
+        <v>1.2</v>
       </c>
       <c r="L40" t="n">
-        <v>73.09</v>
+        <v>65.64</v>
       </c>
       <c r="M40" t="n">
-        <v>1.48</v>
+        <v>2.61</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.098</v>
+        <v>0.133</v>
       </c>
       <c r="Q40" t="n">
-        <v>1504</v>
+        <v>1956</v>
       </c>
       <c r="R40" t="n">
-        <v>13.6</v>
+        <v>20.7</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="T40" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="U40" t="n">
-        <v>18</v>
+        <v>-4</v>
       </c>
       <c r="V40" t="n">
-        <v>4.31</v>
+        <v>2.36</v>
       </c>
       <c r="W40" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="X40" t="n">
-        <v>0.28</v>
+        <v>0.01</v>
       </c>
       <c r="Y40" t="b">
         <v>1</v>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AA40" t="n">
-        <v>267.71</v>
+        <v>183.98</v>
       </c>
       <c r="AB40" t="n">
-        <v>294.76</v>
+        <v>190.89</v>
       </c>
       <c r="AC40" t="n">
-        <v>-12</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4381,96 +4391,86 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>87.76000000000001</v>
+        <v>68.37</v>
       </c>
       <c r="J41" t="n">
-        <v>95.54000000000001</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.1</v>
+        <v>6.8</v>
       </c>
       <c r="L41" t="n">
-        <v>71.72</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>10.87</v>
+        <v>0.31</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.598</v>
+        <v>0.037</v>
       </c>
       <c r="Q41" t="n">
-        <v>1818</v>
+        <v>836</v>
       </c>
       <c r="R41" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="S41" t="n">
-        <v>39</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
-        <v>31</v>
-      </c>
-      <c r="U41" t="n">
-        <v>8</v>
-      </c>
+        <v>12.31</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W41" t="n">
-        <v>11.3</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
-        <v>0.67</v>
+        <v>0.11</v>
       </c>
       <c r="Y41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>12.14</v>
       </c>
       <c r="AA41" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>193.41</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>-45.6</v>
-      </c>
+        <v>66.20999999999999</v>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Euro Pratik Sales Limited</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4481,93 +4481,93 @@
         <v>17</v>
       </c>
       <c r="F42" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I42" t="n">
-        <v>254.05</v>
+        <v>56.65</v>
       </c>
       <c r="J42" t="n">
-        <v>257.65</v>
+        <v>60.15</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.4</v>
+        <v>-5.8</v>
       </c>
       <c r="L42" t="n">
-        <v>70.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>1.64</v>
+        <v>0.9</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.063</v>
+        <v>0.183</v>
       </c>
       <c r="Q42" t="n">
-        <v>2596</v>
+        <v>493</v>
       </c>
       <c r="R42" t="n">
-        <v>45.2</v>
+        <v>12.3</v>
       </c>
       <c r="S42" t="n">
-        <v>-3</v>
+        <v>19</v>
       </c>
       <c r="T42" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="W42" t="n">
-        <v>29.6</v>
+        <v>12</v>
       </c>
       <c r="X42" t="n">
-        <v>0.03</v>
+        <v>0.58</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>24</v>
+        <v>3.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>294.76</v>
+        <v>57.89</v>
       </c>
       <c r="AB42" t="n">
-        <v>278.19</v>
+        <v>59.32</v>
       </c>
       <c r="AC42" t="n">
-        <v>-1.8</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4575,92 +4575,92 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>112.63</v>
+        <v>86.38</v>
       </c>
       <c r="J43" t="n">
-        <v>114.25</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.4</v>
+        <v>-9.6</v>
       </c>
       <c r="L43" t="n">
-        <v>73.48</v>
+        <v>71.72</v>
       </c>
       <c r="M43" t="n">
-        <v>0.43</v>
+        <v>10.87</v>
       </c>
       <c r="N43" t="n">
+        <v>6</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1790</v>
+      </c>
+      <c r="R43" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>39</v>
+      </c>
+      <c r="T43" t="n">
+        <v>31</v>
+      </c>
+      <c r="U43" t="n">
+        <v>8</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W43" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Y43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
         <v>9</v>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>214</v>
-      </c>
-      <c r="R43" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="S43" t="n">
-        <v>21</v>
-      </c>
-      <c r="T43" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="U43" t="n">
-        <v>-29</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W43" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="Y43" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>4.11</v>
-      </c>
       <c r="AA43" t="n">
-        <v>111.71</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="AB43" t="n">
-        <v>120.38</v>
+        <v>191.63</v>
       </c>
       <c r="AC43" t="n">
-        <v>-3.6</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4672,63 +4672,63 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
         <v>14</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>169.92</v>
+        <v>473.95</v>
       </c>
       <c r="J44" t="n">
-        <v>173.91</v>
+        <v>471.92</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.3</v>
+        <v>0.4</v>
       </c>
       <c r="L44" t="n">
-        <v>65.64</v>
+        <v>62.09</v>
       </c>
       <c r="M44" t="n">
-        <v>2.61</v>
+        <v>0.43</v>
       </c>
       <c r="N44" t="n">
         <v>3</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.138</v>
+        <v>0.053</v>
       </c>
       <c r="Q44" t="n">
-        <v>1886</v>
+        <v>813</v>
       </c>
       <c r="R44" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="S44" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="T44" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U44" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>2.36</v>
+        <v>14.66</v>
       </c>
       <c r="W44" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="X44" t="n">
         <v>0.01</v>
@@ -4737,16 +4737,16 @@
         <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AA44" t="n">
-        <v>184.09</v>
+        <v>488.96</v>
       </c>
       <c r="AB44" t="n">
-        <v>191.17</v>
+        <v>489.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>-16.5</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="45">
@@ -4781,13 +4781,13 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>273.3</v>
+        <v>271.35</v>
       </c>
       <c r="J45" t="n">
         <v>292.28</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.5</v>
+        <v>-7.2</v>
       </c>
       <c r="L45" t="n">
         <v>70.45</v>
@@ -4807,10 +4807,10 @@
         <v>0.083</v>
       </c>
       <c r="Q45" t="n">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="R45" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="S45" t="n">
         <v>13</v>
@@ -4837,13 +4837,13 @@
         <v>8</v>
       </c>
       <c r="AA45" t="n">
-        <v>299.6</v>
+        <v>298.79</v>
       </c>
       <c r="AB45" t="n">
-        <v>325.92</v>
+        <v>325.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>-23.1</v>
+        <v>-16.5</v>
       </c>
     </row>
     <row r="46">
@@ -4878,13 +4878,13 @@
         <v>-2</v>
       </c>
       <c r="I46" t="n">
-        <v>30.09</v>
+        <v>29.45</v>
       </c>
       <c r="J46" t="n">
         <v>34.54</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.9</v>
+        <v>-14.7</v>
       </c>
       <c r="L46" t="n">
         <v>61.81</v>
@@ -4901,13 +4901,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.277</v>
+        <v>0.279</v>
       </c>
       <c r="Q46" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="R46" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="S46" t="n">
         <v>16</v>
@@ -4934,28 +4934,28 @@
         <v>1.83</v>
       </c>
       <c r="AA46" t="n">
-        <v>31.32</v>
+        <v>31.21</v>
       </c>
       <c r="AB46" t="n">
-        <v>33.38</v>
+        <v>33.32</v>
       </c>
       <c r="AC46" t="n">
-        <v>-6.3</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>20</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -4975,80 +4975,80 @@
         <v>-2</v>
       </c>
       <c r="I47" t="n">
-        <v>87.12</v>
+        <v>110.82</v>
       </c>
       <c r="J47" t="n">
-        <v>100.33</v>
+        <v>114.25</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.2</v>
+        <v>-3</v>
       </c>
       <c r="L47" t="n">
-        <v>71.89</v>
+        <v>73.48</v>
       </c>
       <c r="M47" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="N47" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="Q47" t="n">
-        <v>888</v>
+        <v>210</v>
       </c>
       <c r="R47" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T47" t="n">
-        <v>18.68</v>
+        <v>12.07</v>
       </c>
       <c r="U47" t="n">
-        <v>-36</v>
+        <v>-29</v>
       </c>
       <c r="V47" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>6.79</v>
+        <v>7.92</v>
       </c>
       <c r="X47" t="n">
-        <v>0.26</v>
+        <v>0.98</v>
       </c>
       <c r="Y47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.02</v>
+        <v>4.11</v>
       </c>
       <c r="AA47" t="n">
-        <v>92.81</v>
+        <v>111.55</v>
       </c>
       <c r="AB47" t="n">
-        <v>104.6</v>
+        <v>120.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>-26.8</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -5060,81 +5060,81 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F48" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I48" t="n">
-        <v>468.75</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>471.65</v>
+        <v>100.33</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.6</v>
+        <v>-14.5</v>
       </c>
       <c r="L48" t="n">
-        <v>62.09</v>
+        <v>71.89</v>
       </c>
       <c r="M48" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.039</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>805</v>
+        <v>873</v>
       </c>
       <c r="R48" t="n">
-        <v>7.91</v>
+        <v>23.8</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>30</v>
+        <v>18.68</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="V48" t="n">
-        <v>14.66</v>
+        <v>0.85</v>
       </c>
       <c r="W48" t="n">
-        <v>14.4</v>
+        <v>6.79</v>
       </c>
       <c r="X48" t="n">
-        <v>0.01</v>
+        <v>0.26</v>
       </c>
       <c r="Y48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>14</v>
+        <v>4.02</v>
       </c>
       <c r="AA48" t="n">
-        <v>489.29</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="AB48" t="n">
-        <v>489.35</v>
+        <v>104.38</v>
       </c>
       <c r="AC48" t="n">
-        <v>-2.7</v>
+        <v>-26.2</v>
       </c>
     </row>
   </sheetData>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>254.85</v>
+        <v>256.47</v>
       </c>
       <c r="D2" t="n">
         <v>158.6</v>
       </c>
       <c r="E2" t="n">
-        <v>60.7</v>
+        <v>61.7</v>
       </c>
       <c r="F2" t="n">
         <v>64.63</v>
@@ -5256,13 +5256,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>95.20999999999999</v>
+        <v>93.86</v>
       </c>
       <c r="D3" t="n">
         <v>55.78</v>
       </c>
       <c r="E3" t="n">
-        <v>70.7</v>
+        <v>68.3</v>
       </c>
       <c r="F3" t="n">
         <v>67.45999999999999</v>
@@ -5282,245 +5282,245 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>MACPOWER CNC MACHINES LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5502</v>
+        <v>2007.1</v>
       </c>
       <c r="D4" t="n">
-        <v>5187.29</v>
+        <v>920.51</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
-        <v>67.16</v>
+        <v>73.16</v>
       </c>
       <c r="G4" t="n">
-        <v>6.71</v>
+        <v>0.44</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MACPOWER CNC MACHINES LIMITED</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1868.8</v>
+        <v>238.75</v>
       </c>
       <c r="D5" t="n">
-        <v>920.51</v>
+        <v>217.8</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>9.6</v>
       </c>
       <c r="F5" t="n">
-        <v>73.16</v>
+        <v>71.75</v>
       </c>
       <c r="G5" t="n">
-        <v>0.44</v>
+        <v>0.82</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>824</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>752.23</v>
+        <v>70.27</v>
       </c>
       <c r="E6" t="n">
-        <v>9.5</v>
+        <v>2.1</v>
       </c>
       <c r="F6" t="n">
-        <v>69.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>15.13</v>
+        <v>0.7</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THANGAMAIYL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>71.66</v>
+        <v>5440.5</v>
       </c>
       <c r="D7" t="n">
-        <v>70.27</v>
+        <v>5187.29</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="F7" t="n">
-        <v>72.56999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7</v>
+        <v>6.71</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>227.39</v>
+        <v>813.45</v>
       </c>
       <c r="D8" t="n">
-        <v>217.8</v>
+        <v>752.23</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="F8" t="n">
-        <v>71.75</v>
+        <v>69.61</v>
       </c>
       <c r="G8" t="n">
-        <v>0.82</v>
+        <v>15.13</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>362.75</v>
+        <v>542.25</v>
       </c>
       <c r="D9" t="n">
-        <v>335.41</v>
+        <v>390.61</v>
       </c>
       <c r="E9" t="n">
-        <v>8.199999999999999</v>
+        <v>38.8</v>
       </c>
       <c r="F9" t="n">
-        <v>68.48</v>
+        <v>63.09</v>
       </c>
       <c r="G9" t="n">
-        <v>0.41</v>
+        <v>8.02</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>542.9</v>
+        <v>192.36</v>
       </c>
       <c r="D10" t="n">
-        <v>390.61</v>
+        <v>164.1</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>17.2</v>
       </c>
       <c r="F10" t="n">
-        <v>63.09</v>
+        <v>60.6</v>
       </c>
       <c r="G10" t="n">
-        <v>8.02</v>
+        <v>0.25</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
@@ -5536,13 +5536,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>269.84</v>
+        <v>267.49</v>
       </c>
       <c r="D11" t="n">
         <v>243.52</v>
       </c>
       <c r="E11" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F11" t="n">
         <v>67.65000000000001</v>
@@ -5562,105 +5562,105 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>191.06</v>
+        <v>366.7</v>
       </c>
       <c r="D12" t="n">
-        <v>164.1</v>
+        <v>338.1</v>
       </c>
       <c r="E12" t="n">
-        <v>16.4</v>
+        <v>8.5</v>
       </c>
       <c r="F12" t="n">
-        <v>60.6</v>
+        <v>66.73</v>
       </c>
       <c r="G12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>365.9</v>
+        <v>354.85</v>
       </c>
       <c r="D13" t="n">
-        <v>338.1</v>
+        <v>335.41</v>
       </c>
       <c r="E13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="F13" t="n">
-        <v>66.73</v>
+        <v>68.48</v>
       </c>
       <c r="G13" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>622.6</v>
+        <v>331.05</v>
       </c>
       <c r="D14" t="n">
-        <v>567.47</v>
+        <v>311.69</v>
       </c>
       <c r="E14" t="n">
-        <v>9.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="F14" t="n">
-        <v>64.68000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="G14" t="n">
-        <v>5.47</v>
+        <v>1.41</v>
       </c>
       <c r="H14" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
     </row>
@@ -5702,105 +5702,105 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.1</v>
+        <v>636.9</v>
       </c>
       <c r="D16" t="n">
-        <v>21.01</v>
+        <v>567.47</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.3</v>
+        <v>12.2</v>
       </c>
       <c r="F16" t="n">
-        <v>70.87</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>5.47</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>79.92</v>
+        <v>19.86</v>
       </c>
       <c r="D17" t="n">
-        <v>74.92</v>
+        <v>21.01</v>
       </c>
       <c r="E17" t="n">
-        <v>6.7</v>
+        <v>-5.5</v>
       </c>
       <c r="F17" t="n">
-        <v>62.78</v>
+        <v>70.87</v>
       </c>
       <c r="G17" t="n">
-        <v>1.48</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>102.77</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>89.34</v>
+        <v>74.92</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>70.88</v>
+        <v>62.78</v>
       </c>
       <c r="G18" t="n">
-        <v>6.25</v>
+        <v>1.48</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
@@ -5816,13 +5816,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>133.81</v>
+        <v>139.39</v>
       </c>
       <c r="D19" t="n">
         <v>100.9</v>
       </c>
       <c r="E19" t="n">
-        <v>32.6</v>
+        <v>38.1</v>
       </c>
       <c r="F19" t="n">
         <v>69.56</v>
@@ -5842,525 +5842,525 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>319.9</v>
+        <v>100.04</v>
       </c>
       <c r="D20" t="n">
-        <v>311.69</v>
+        <v>89.34</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>63.24</v>
+        <v>70.88</v>
       </c>
       <c r="G20" t="n">
-        <v>1.41</v>
+        <v>6.25</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OBCL LIMITED (FORMERLY KNOWN AS ORISSA BENGAL CARRIER LIMITED)</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>56.16</v>
+        <v>213</v>
       </c>
       <c r="D21" t="n">
-        <v>53.44</v>
+        <v>209.98</v>
       </c>
       <c r="E21" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="F21" t="n">
-        <v>67.23</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>1.88</v>
+        <v>0.26</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>212.68</v>
+        <v>1316.1</v>
       </c>
       <c r="D22" t="n">
-        <v>209.98</v>
+        <v>1104.34</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3</v>
+        <v>19.2</v>
       </c>
       <c r="F22" t="n">
-        <v>67.04000000000001</v>
+        <v>60.82</v>
       </c>
       <c r="G22" t="n">
-        <v>0.26</v>
+        <v>5.22</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1282</v>
+        <v>122.81</v>
       </c>
       <c r="D23" t="n">
-        <v>1104.34</v>
+        <v>105.19</v>
       </c>
       <c r="E23" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="F23" t="n">
-        <v>60.82</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>5.22</v>
+        <v>2.63</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>115.46</v>
+        <v>13.9</v>
       </c>
       <c r="D24" t="n">
-        <v>105.19</v>
+        <v>12.31</v>
       </c>
       <c r="E24" t="n">
-        <v>9.800000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="F24" t="n">
-        <v>67.15000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="G24" t="n">
-        <v>2.63</v>
+        <v>1.35</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13.68</v>
+        <v>55.4</v>
       </c>
       <c r="D25" t="n">
-        <v>12.28</v>
+        <v>53.44</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4</v>
+        <v>3.7</v>
       </c>
       <c r="F25" t="n">
-        <v>69.12</v>
+        <v>67.23</v>
       </c>
       <c r="G25" t="n">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>110.06</v>
+        <v>322</v>
       </c>
       <c r="D26" t="n">
-        <v>109.31</v>
+        <v>297.3</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>72.34</v>
+        <v>67.69</v>
       </c>
       <c r="G26" t="n">
-        <v>48.4</v>
+        <v>2.97</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>320.9</v>
+        <v>178.22</v>
       </c>
       <c r="D27" t="n">
-        <v>297.3</v>
+        <v>180.98</v>
       </c>
       <c r="E27" t="n">
-        <v>7.9</v>
+        <v>-1.5</v>
       </c>
       <c r="F27" t="n">
-        <v>67.69</v>
+        <v>74.59</v>
       </c>
       <c r="G27" t="n">
-        <v>2.97</v>
+        <v>0.25</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>43.09</v>
+        <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>43.04</v>
+        <v>29.14</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1</v>
+        <v>-7.3</v>
       </c>
       <c r="F28" t="n">
-        <v>71.79000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="G28" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="H28" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.81</v>
+        <v>174.15</v>
       </c>
       <c r="D29" t="n">
-        <v>29.14</v>
+        <v>201.21</v>
       </c>
       <c r="E29" t="n">
-        <v>-8</v>
+        <v>-13.4</v>
       </c>
       <c r="F29" t="n">
-        <v>69.03</v>
+        <v>64.08</v>
       </c>
       <c r="G29" t="n">
-        <v>1.34</v>
+        <v>8.07</v>
       </c>
       <c r="H29" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>178.58</v>
+        <v>744.75</v>
       </c>
       <c r="D30" t="n">
-        <v>180.98</v>
+        <v>717.77</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.3</v>
+        <v>3.8</v>
       </c>
       <c r="F30" t="n">
-        <v>74.59</v>
+        <v>61.71</v>
       </c>
       <c r="G30" t="n">
-        <v>0.25</v>
+        <v>1.61</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>163.49</v>
+        <v>175.31</v>
       </c>
       <c r="D31" t="n">
-        <v>204.13</v>
+        <v>182.69</v>
       </c>
       <c r="E31" t="n">
-        <v>-19.9</v>
+        <v>-4</v>
       </c>
       <c r="F31" t="n">
-        <v>64.08</v>
+        <v>69.05</v>
       </c>
       <c r="G31" t="n">
-        <v>7.57</v>
+        <v>0.74</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>172.27</v>
+        <v>108.43</v>
       </c>
       <c r="D32" t="n">
-        <v>182.69</v>
+        <v>109.31</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.7</v>
+        <v>-0.8</v>
       </c>
       <c r="F32" t="n">
-        <v>69.05</v>
+        <v>72.34</v>
       </c>
       <c r="G32" t="n">
-        <v>0.74</v>
+        <v>48.4</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>751.85</v>
+        <v>509.7</v>
       </c>
       <c r="D33" t="n">
-        <v>717.77</v>
+        <v>545.03</v>
       </c>
       <c r="E33" t="n">
-        <v>4.7</v>
+        <v>-6.5</v>
       </c>
       <c r="F33" t="n">
-        <v>61.71</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>517.05</v>
+        <v>42.46</v>
       </c>
       <c r="D34" t="n">
-        <v>545.03</v>
+        <v>43.04</v>
       </c>
       <c r="E34" t="n">
-        <v>-5.1</v>
+        <v>-1.3</v>
       </c>
       <c r="F34" t="n">
-        <v>69.90000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
@@ -6376,13 +6376,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>116.98</v>
+        <v>117.41</v>
       </c>
       <c r="D35" t="n">
         <v>114.86</v>
       </c>
       <c r="E35" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="F35" t="n">
         <v>69.73999999999999</v>
@@ -6402,315 +6402,315 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>729.3</v>
+        <v>268.7</v>
       </c>
       <c r="D36" t="n">
-        <v>815.16</v>
+        <v>269.7</v>
       </c>
       <c r="E36" t="n">
-        <v>-10.5</v>
+        <v>-0.4</v>
       </c>
       <c r="F36" t="n">
-        <v>73.2</v>
+        <v>73.09</v>
       </c>
       <c r="G36" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>433.85</v>
+        <v>728.4</v>
       </c>
       <c r="D37" t="n">
-        <v>474.82</v>
+        <v>815.16</v>
       </c>
       <c r="E37" t="n">
-        <v>-8.6</v>
+        <v>-10.6</v>
       </c>
       <c r="F37" t="n">
-        <v>70.55</v>
+        <v>73.2</v>
       </c>
       <c r="G37" t="n">
-        <v>10.22</v>
+        <v>1.24</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69.16</v>
+        <v>434.15</v>
       </c>
       <c r="D38" t="n">
-        <v>64.04000000000001</v>
+        <v>474.82</v>
       </c>
       <c r="E38" t="n">
-        <v>8</v>
+        <v>-8.6</v>
       </c>
       <c r="F38" t="n">
-        <v>64.29000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="G38" t="n">
-        <v>0.31</v>
+        <v>10.22</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>EUROPRATIK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>Euro Pratik Sales Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>56.95</v>
+        <v>257.45</v>
       </c>
       <c r="D39" t="n">
-        <v>60.15</v>
+        <v>257.65</v>
       </c>
       <c r="E39" t="n">
-        <v>-5.3</v>
+        <v>-0.1</v>
       </c>
       <c r="F39" t="n">
-        <v>73.01000000000001</v>
+        <v>70.09</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9</v>
+        <v>1.64</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>265.25</v>
+        <v>175.95</v>
       </c>
       <c r="D40" t="n">
-        <v>269.7</v>
+        <v>173.91</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6</v>
+        <v>1.2</v>
       </c>
       <c r="F40" t="n">
-        <v>73.09</v>
+        <v>65.64</v>
       </c>
       <c r="G40" t="n">
-        <v>1.48</v>
+        <v>2.61</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>87.76000000000001</v>
+        <v>68.37</v>
       </c>
       <c r="D41" t="n">
-        <v>95.54000000000001</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>-8.1</v>
+        <v>6.8</v>
       </c>
       <c r="F41" t="n">
-        <v>71.72</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>10.87</v>
+        <v>0.31</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Euro Pratik Sales Limited</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>254.05</v>
+        <v>56.65</v>
       </c>
       <c r="D42" t="n">
-        <v>257.65</v>
+        <v>60.15</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.4</v>
+        <v>-5.8</v>
       </c>
       <c r="F42" t="n">
-        <v>70.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>1.64</v>
+        <v>0.9</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>112.63</v>
+        <v>86.38</v>
       </c>
       <c r="D43" t="n">
-        <v>114.25</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.4</v>
+        <v>-9.6</v>
       </c>
       <c r="F43" t="n">
-        <v>73.48</v>
+        <v>71.72</v>
       </c>
       <c r="G43" t="n">
-        <v>0.43</v>
+        <v>10.87</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>169.92</v>
+        <v>473.95</v>
       </c>
       <c r="D44" t="n">
-        <v>173.91</v>
+        <v>471.92</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.3</v>
+        <v>0.4</v>
       </c>
       <c r="F44" t="n">
-        <v>65.64</v>
+        <v>62.09</v>
       </c>
       <c r="G44" t="n">
-        <v>2.61</v>
+        <v>0.43</v>
       </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
@@ -6726,13 +6726,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>273.3</v>
+        <v>271.35</v>
       </c>
       <c r="D45" t="n">
         <v>292.28</v>
       </c>
       <c r="E45" t="n">
-        <v>-6.5</v>
+        <v>-7.2</v>
       </c>
       <c r="F45" t="n">
         <v>70.45</v>
@@ -6761,13 +6761,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>30.09</v>
+        <v>29.45</v>
       </c>
       <c r="D46" t="n">
         <v>34.54</v>
       </c>
       <c r="E46" t="n">
-        <v>-12.9</v>
+        <v>-14.7</v>
       </c>
       <c r="F46" t="n">
         <v>61.81</v>
@@ -6787,70 +6787,70 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>87.12</v>
+        <v>110.82</v>
       </c>
       <c r="D47" t="n">
-        <v>100.33</v>
+        <v>114.25</v>
       </c>
       <c r="E47" t="n">
-        <v>-13.2</v>
+        <v>-3</v>
       </c>
       <c r="F47" t="n">
-        <v>71.89</v>
+        <v>73.48</v>
       </c>
       <c r="G47" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>468.75</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>471.65</v>
+        <v>100.33</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6</v>
+        <v>-14.5</v>
       </c>
       <c r="F48" t="n">
-        <v>62.09</v>
+        <v>71.89</v>
       </c>
       <c r="G48" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/2026-08-28/enriched_analysis.xlsx
+++ b/output/2026-08-28/enriched_analysis.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
         <v>30.8</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="b">
         <v>1</v>
@@ -805,16 +805,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>MACPOWER CNC MACHINES LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -822,96 +822,96 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5440.5</v>
+        <v>2007.1</v>
       </c>
       <c r="J4" t="n">
-        <v>5187.29</v>
+        <v>920.51</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>118</v>
       </c>
       <c r="L4" t="n">
-        <v>67.16</v>
+        <v>73.16</v>
       </c>
       <c r="M4" t="n">
-        <v>6.71</v>
+        <v>0.44</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.04</v>
+        <v>0.022</v>
       </c>
       <c r="Q4" t="n">
-        <v>16910</v>
+        <v>2008</v>
       </c>
       <c r="R4" t="n">
-        <v>43.1</v>
+        <v>51.6</v>
       </c>
       <c r="S4" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="T4" t="n">
-        <v>145</v>
+        <v>15.42</v>
       </c>
       <c r="U4" t="n">
-        <v>264</v>
+        <v>47</v>
       </c>
       <c r="V4" t="n">
-        <v>27.38</v>
+        <v>9.58</v>
       </c>
       <c r="W4" t="n">
-        <v>25.5</v>
+        <v>29.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.64</v>
+        <v>0.01</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>16.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>5883.33</v>
+        <v>1512.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>4274.66</v>
+        <v>1109.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>51.4</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -925,379 +925,381 @@
         <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>813.45</v>
+        <v>238.75</v>
       </c>
       <c r="J5" t="n">
-        <v>745.6900000000001</v>
+        <v>217.8</v>
       </c>
       <c r="K5" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="L5" t="n">
-        <v>69.61</v>
+        <v>71.75</v>
       </c>
       <c r="M5" t="n">
-        <v>9.18</v>
+        <v>0.82</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.057</v>
+        <v>0.079</v>
       </c>
       <c r="Q5" t="n">
-        <v>15989</v>
+        <v>1042</v>
       </c>
       <c r="R5" t="n">
-        <v>20.3</v>
+        <v>14</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="T5" t="n">
-        <v>346</v>
+        <v>40</v>
       </c>
       <c r="U5" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="V5" t="n">
-        <v>10.02</v>
+        <v>8.23</v>
       </c>
       <c r="W5" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>816.71</v>
+        <v>213.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>792.34</v>
+        <v>180.81</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.7</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Buy on Breakout</t>
+          <t>Strong Buy Setup</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>542.25</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>390.61</v>
+        <v>70.19</v>
       </c>
       <c r="K6" t="n">
-        <v>38.8</v>
+        <v>2.2</v>
       </c>
       <c r="L6" t="n">
-        <v>63.09</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>8.02</v>
+        <v>0.91</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.467</v>
+        <v>0.431</v>
       </c>
       <c r="Q6" t="n">
-        <v>1719</v>
+        <v>211</v>
       </c>
       <c r="R6" t="n">
-        <v>20.4</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>581</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
-        <v>34</v>
+        <v>27.97</v>
       </c>
       <c r="U6" t="n">
-        <v>881</v>
+        <v>17</v>
       </c>
       <c r="V6" t="n">
-        <v>8.58</v>
+        <v>2.73</v>
       </c>
       <c r="W6" t="n">
-        <v>22</v>
+        <v>13.7</v>
       </c>
       <c r="X6" t="n">
-        <v>0.33</v>
+        <v>1.86</v>
       </c>
       <c r="Y6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>29</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>463.54</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+        <v>55.56</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>51.3</v>
+      </c>
       <c r="AC6" t="n">
-        <v>31.7</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Buy on Breakout</t>
+          <t>Strong Buy Setup</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>636.9</v>
+        <v>5440.5</v>
       </c>
       <c r="J7" t="n">
-        <v>567.47</v>
+        <v>5187.29</v>
       </c>
       <c r="K7" t="n">
-        <v>12.2</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>64.68000000000001</v>
+        <v>67.16</v>
       </c>
       <c r="M7" t="n">
-        <v>5.47</v>
+        <v>6.71</v>
       </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.466</v>
+        <v>0.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1175</v>
+        <v>16910</v>
       </c>
       <c r="R7" t="n">
-        <v>59.9</v>
+        <v>43.1</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.11</v>
+        <v>145</v>
       </c>
       <c r="U7" t="n">
-        <v>23</v>
+        <v>264</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>27.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>25.5</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="Y7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>-110</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>572.55</v>
+        <v>5883.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>504.68</v>
+        <v>4274.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>33</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Buy on Breakout</t>
+          <t>Strong Buy Setup</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>331.05</v>
+        <v>813.45</v>
       </c>
       <c r="J8" t="n">
-        <v>311.69</v>
+        <v>745.6900000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>9.1</v>
       </c>
       <c r="L8" t="n">
-        <v>63.24</v>
+        <v>69.61</v>
       </c>
       <c r="M8" t="n">
-        <v>1.41</v>
+        <v>9.18</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.446</v>
+        <v>0.057</v>
       </c>
       <c r="Q8" t="n">
-        <v>316</v>
+        <v>15989</v>
       </c>
       <c r="R8" t="n">
-        <v>146</v>
+        <v>20.3</v>
       </c>
       <c r="S8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>346</v>
       </c>
       <c r="U8" t="n">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="V8" t="n">
-        <v>2.55</v>
+        <v>10.02</v>
       </c>
       <c r="W8" t="n">
-        <v>2.07</v>
+        <v>12.3</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="Y8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.06</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>289.92</v>
+        <v>816.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>276.49</v>
+        <v>792.34</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1308,93 +1310,91 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>81.51000000000001</v>
+        <v>542.25</v>
       </c>
       <c r="J9" t="n">
-        <v>74.92</v>
+        <v>390.61</v>
       </c>
       <c r="K9" t="n">
-        <v>8.800000000000001</v>
+        <v>38.8</v>
       </c>
       <c r="L9" t="n">
-        <v>62.78</v>
+        <v>63.09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.48</v>
+        <v>8.02</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.354</v>
+        <v>0.467</v>
       </c>
       <c r="Q9" t="n">
-        <v>418</v>
+        <v>1719</v>
       </c>
       <c r="R9" t="n">
-        <v>38.8</v>
+        <v>20.4</v>
       </c>
       <c r="S9" t="n">
-        <v>21</v>
+        <v>581</v>
       </c>
       <c r="T9" t="n">
-        <v>8.390000000000001</v>
+        <v>34</v>
       </c>
       <c r="U9" t="n">
-        <v>-19</v>
+        <v>881</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>8.58</v>
       </c>
       <c r="W9" t="n">
-        <v>8.73</v>
+        <v>22</v>
       </c>
       <c r="X9" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="Y9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>41.64</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>75.75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>78.34</v>
-      </c>
+        <v>463.54</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>10.6</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,28 +1405,28 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I10" t="n">
-        <v>100.04</v>
+        <v>267.49</v>
       </c>
       <c r="J10" t="n">
-        <v>89.34</v>
+        <v>243.52</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>70.88</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>6.25</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1437,61 +1437,61 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.243</v>
+        <v>0.154</v>
       </c>
       <c r="Q10" t="n">
-        <v>2569</v>
+        <v>719</v>
       </c>
       <c r="R10" t="n">
-        <v>21</v>
+        <v>60.1</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>14</v>
+        <v>2.99</v>
       </c>
       <c r="U10" t="n">
-        <v>-14</v>
+        <v>97</v>
       </c>
       <c r="V10" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>16.9</v>
+        <v>11.6</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>16.21</v>
       </c>
       <c r="AA10" t="n">
-        <v>90.28</v>
+        <v>245.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>92</v>
+        <v>177.97</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.6</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1502,93 +1502,93 @@
         <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>139.39</v>
+        <v>354.85</v>
       </c>
       <c r="J11" t="n">
-        <v>100.9</v>
+        <v>335.41</v>
       </c>
       <c r="K11" t="n">
-        <v>38.1</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
-        <v>69.56</v>
+        <v>68.48</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>0.41</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.201</v>
+        <v>0.007</v>
       </c>
       <c r="Q11" t="n">
-        <v>1497</v>
+        <v>5816</v>
       </c>
       <c r="R11" t="n">
-        <v>52.2</v>
+        <v>9.83</v>
       </c>
       <c r="S11" t="n">
+        <v>43</v>
+      </c>
+      <c r="T11" t="n">
+        <v>223</v>
+      </c>
+      <c r="U11" t="n">
+        <v>175</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="W11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
         <v>7</v>
       </c>
-      <c r="T11" t="n">
-        <v>22</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W11" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="Y11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5</v>
-      </c>
       <c r="AA11" t="n">
-        <v>121.02</v>
+        <v>362.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>115.44</v>
+        <v>333.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>23.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1596,96 +1596,96 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1316.1</v>
+        <v>366.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1104.34</v>
+        <v>338.1</v>
       </c>
       <c r="K12" t="n">
-        <v>19.2</v>
+        <v>8.5</v>
       </c>
       <c r="L12" t="n">
-        <v>60.82</v>
+        <v>66.73</v>
       </c>
       <c r="M12" t="n">
-        <v>5.22</v>
+        <v>0.34</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.001</v>
+        <v>0.079</v>
       </c>
       <c r="Q12" t="n">
-        <v>357145</v>
+        <v>432</v>
       </c>
       <c r="R12" t="n">
-        <v>19.6</v>
+        <v>12.8</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>-8</v>
       </c>
       <c r="T12" t="n">
-        <v>4158</v>
+        <v>24</v>
       </c>
       <c r="U12" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="V12" t="n">
-        <v>25.89</v>
+        <v>14.36</v>
       </c>
       <c r="W12" t="n">
-        <v>53.4</v>
+        <v>9.94</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>1246.07</v>
+        <v>316.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>1396.25</v>
+        <v>259</v>
       </c>
       <c r="AC12" t="n">
-        <v>-7.7</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1693,92 +1693,94 @@
         </is>
       </c>
       <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>23</v>
+      </c>
+      <c r="G13" t="n">
         <v>25</v>
       </c>
-      <c r="F13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>20</v>
-      </c>
       <c r="H13" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>13.9</v>
+        <v>192.36</v>
       </c>
       <c r="J13" t="n">
-        <v>12.31</v>
+        <v>164.1</v>
       </c>
       <c r="K13" t="n">
-        <v>12.9</v>
+        <v>17.2</v>
       </c>
       <c r="L13" t="n">
-        <v>69.12</v>
+        <v>60.6</v>
       </c>
       <c r="M13" t="n">
-        <v>1.35</v>
+        <v>0.25</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.344</v>
+        <v>0.006</v>
       </c>
       <c r="Q13" t="n">
-        <v>392</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1265</v>
-      </c>
+        <v>4078</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="T13" t="n">
+        <v>258</v>
+      </c>
       <c r="U13" t="n">
-        <v>-98</v>
+        <v>30</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01</v>
+        <v>-1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>2.46</v>
+        <v>6.38</v>
       </c>
       <c r="X13" t="n">
-        <v>0.44</v>
+        <v>10.11</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
       </c>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>61</v>
+      </c>
       <c r="AA13" t="n">
-        <v>11.06</v>
+        <v>177.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>13.55</v>
+        <v>178.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>-7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1786,612 +1788,612 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I14" t="n">
-        <v>122.81</v>
+        <v>636.9</v>
       </c>
       <c r="J14" t="n">
-        <v>105.19</v>
+        <v>567.47</v>
       </c>
       <c r="K14" t="n">
-        <v>16.8</v>
+        <v>12.2</v>
       </c>
       <c r="L14" t="n">
-        <v>67.15000000000001</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>2.63</v>
+        <v>5.47</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.053</v>
+        <v>0.466</v>
       </c>
       <c r="Q14" t="n">
-        <v>4957</v>
+        <v>1175</v>
       </c>
       <c r="R14" t="n">
-        <v>32.3</v>
+        <v>59.9</v>
       </c>
       <c r="S14" t="n">
-        <v>-25</v>
+        <v>21</v>
       </c>
       <c r="T14" t="n">
-        <v>71</v>
+        <v>-0.11</v>
       </c>
       <c r="U14" t="n">
-        <v>-11</v>
+        <v>23</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>10.7</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>69</v>
+        <v>-110</v>
       </c>
       <c r="AA14" t="n">
-        <v>105.35</v>
+        <v>572.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>112.38</v>
+        <v>504.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OBCL LIMITED (FORMERLY KNOWN AS ORISSA BENGAL CARRIER LIMITED)</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I15" t="n">
-        <v>55.4</v>
+        <v>331.05</v>
       </c>
       <c r="J15" t="n">
-        <v>53.44</v>
+        <v>311.69</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
-        <v>67.23</v>
+        <v>63.24</v>
       </c>
       <c r="M15" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="N15" t="n">
         <v>7</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.607</v>
+        <v>0.446</v>
       </c>
       <c r="Q15" t="n">
-        <v>117</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
+        <v>316</v>
+      </c>
+      <c r="R15" t="n">
+        <v>146</v>
+      </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>-3779</v>
+        <v>264</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.05</v>
+        <v>2.55</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.26</v>
+        <v>2.07</v>
       </c>
       <c r="X15" t="n">
-        <v>0.8</v>
+        <v>0.01</v>
       </c>
       <c r="Y15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>6.06</v>
       </c>
       <c r="AA15" t="n">
-        <v>54.27</v>
+        <v>289.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>55.13</v>
+        <v>276.49</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>125</v>
+      </c>
+      <c r="J16" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>863</v>
+      </c>
+      <c r="R16" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U16" t="n">
+        <v>82</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W16" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>322</v>
-      </c>
-      <c r="J16" t="n">
-        <v>297.3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L16" t="n">
-        <v>67.69</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>12-06-2026</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1084</v>
-      </c>
-      <c r="R16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>12</v>
-      </c>
-      <c r="T16" t="n">
-        <v>29</v>
-      </c>
-      <c r="U16" t="n">
-        <v>20</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="W16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.47</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>3.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>333.76</v>
+        <v>105.42</v>
       </c>
       <c r="AB16" t="n">
-        <v>349.79</v>
+        <v>69.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.5</v>
+        <v>138.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>19.86</v>
       </c>
       <c r="J17" t="n">
-        <v>29.14</v>
+        <v>21.01</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.3</v>
+        <v>-5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>69.03</v>
+        <v>70.87</v>
       </c>
       <c r="M17" t="n">
-        <v>1.34</v>
+        <v>0.5</v>
       </c>
       <c r="N17" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.276</v>
+        <v>0.132</v>
       </c>
       <c r="Q17" t="n">
-        <v>105</v>
+        <v>378</v>
       </c>
       <c r="R17" t="n">
-        <v>75.2</v>
+        <v>6.1</v>
       </c>
       <c r="S17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.4</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>26</v>
+        <v>391</v>
       </c>
       <c r="V17" t="n">
-        <v>0.59</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.18</v>
+        <v>18.5</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y17" t="b">
         <v>0</v>
       </c>
-      <c r="Z17" t="n">
-        <v>21.51</v>
-      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
-        <v>27.41</v>
+        <v>17.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>24.6</v>
+        <v>15.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>24.8</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>20</v>
       </c>
       <c r="F18" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" t="n">
         <v>25</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>174.15</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>201.21</v>
+        <v>76.98</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.4</v>
+        <v>5.9</v>
       </c>
       <c r="L18" t="n">
-        <v>64.08</v>
+        <v>62.78</v>
       </c>
       <c r="M18" t="n">
-        <v>8.07</v>
+        <v>2.64</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.146</v>
+        <v>0.632</v>
       </c>
       <c r="Q18" t="n">
-        <v>704</v>
+        <v>418</v>
       </c>
       <c r="R18" t="n">
-        <v>15.5</v>
+        <v>38.8</v>
       </c>
       <c r="S18" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="T18" t="n">
-        <v>21</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>45</v>
+        <v>-19</v>
       </c>
       <c r="V18" t="n">
-        <v>3.1</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>19.4</v>
+        <v>8.73</v>
       </c>
       <c r="X18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="Y18" t="b">
         <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>11</v>
+        <v>41.64</v>
       </c>
       <c r="AA18" t="n">
-        <v>177.46</v>
+        <v>75.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>200.72</v>
+        <v>78.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>744.75</v>
+        <v>100.04</v>
       </c>
       <c r="J19" t="n">
-        <v>717.77</v>
+        <v>89.34</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>61.71</v>
+        <v>70.88</v>
       </c>
       <c r="M19" t="n">
-        <v>1.61</v>
+        <v>6.25</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.697</v>
+        <v>0.243</v>
       </c>
       <c r="Q19" t="n">
-        <v>231</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
+        <v>2569</v>
+      </c>
+      <c r="R19" t="n">
+        <v>21</v>
+      </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>11.91</v>
+        <v>14</v>
       </c>
       <c r="U19" t="n">
-        <v>-184</v>
+        <v>-14</v>
       </c>
       <c r="V19" t="n">
-        <v>31.98</v>
+        <v>0.57</v>
       </c>
       <c r="W19" t="n">
-        <v>0.27</v>
+        <v>16.9</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>57.93</v>
+        <v>30</v>
       </c>
       <c r="AA19" t="n">
-        <v>731.34</v>
+        <v>90.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>760.58</v>
+        <v>92</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>108.43</v>
+        <v>139.39</v>
       </c>
       <c r="J20" t="n">
-        <v>109.31</v>
+        <v>100.9</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8</v>
+        <v>38.1</v>
       </c>
       <c r="L20" t="n">
-        <v>72.34</v>
+        <v>69.56</v>
       </c>
       <c r="M20" t="n">
-        <v>48.4</v>
+        <v>3.01</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2399,31 +2401,31 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.949</v>
+        <v>0.201</v>
       </c>
       <c r="Q20" t="n">
-        <v>5100</v>
+        <v>1497</v>
       </c>
       <c r="R20" t="n">
-        <v>40.9</v>
+        <v>52.2</v>
       </c>
       <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>22</v>
+      </c>
+      <c r="U20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="n">
-        <v>42</v>
-      </c>
-      <c r="U20" t="n">
-        <v>8</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0.95</v>
       </c>
       <c r="W20" t="n">
-        <v>9.710000000000001</v>
+        <v>5.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0.06</v>
+        <v>0.52</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
@@ -2432,595 +2434,2707 @@
         <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>105.55</v>
+        <v>121.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>114.25</v>
+        <v>115.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.8</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AJMERA</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>25</v>
       </c>
-      <c r="F21" t="n">
-        <v>13</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I21" t="n">
-        <v>117.41</v>
+        <v>213</v>
       </c>
       <c r="J21" t="n">
-        <v>114.86</v>
+        <v>209.98</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="L21" t="n">
-        <v>69.73999999999999</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>7.36</v>
+        <v>0.26</v>
       </c>
       <c r="N21" t="n">
         <v>4</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.318</v>
+        <v>0.131</v>
       </c>
       <c r="Q21" t="n">
-        <v>2311</v>
+        <v>199</v>
       </c>
       <c r="R21" t="n">
-        <v>19.8</v>
+        <v>24.8</v>
       </c>
       <c r="S21" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>46</v>
+        <v>0.03</v>
       </c>
       <c r="U21" t="n">
-        <v>-4</v>
+        <v>16</v>
       </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>0.03</v>
       </c>
       <c r="W21" t="n">
-        <v>14.2</v>
+        <v>7.91</v>
       </c>
       <c r="X21" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="b">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>38</v>
+        <v>3.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>126.3</v>
+        <v>206.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>327.83</v>
+        <v>194.89</v>
       </c>
       <c r="AC21" t="n">
-        <v>-12.3</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>268.7</v>
+        <v>1316.1</v>
       </c>
       <c r="J22" t="n">
-        <v>269.7</v>
+        <v>1104.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4</v>
+        <v>19.2</v>
       </c>
       <c r="L22" t="n">
-        <v>73.09</v>
+        <v>60.82</v>
       </c>
       <c r="M22" t="n">
-        <v>1.48</v>
+        <v>5.22</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.097</v>
+        <v>0.001</v>
       </c>
       <c r="Q22" t="n">
-        <v>1524</v>
+        <v>357145</v>
       </c>
       <c r="R22" t="n">
-        <v>13.8</v>
+        <v>19.6</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>46</v>
+        <v>4158</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="V22" t="n">
-        <v>4.31</v>
+        <v>25.89</v>
       </c>
       <c r="W22" t="n">
-        <v>13.6</v>
+        <v>53.4</v>
       </c>
       <c r="X22" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AA22" t="n">
-        <v>267.86</v>
+        <v>1246.07</v>
       </c>
       <c r="AB22" t="n">
-        <v>294.37</v>
+        <v>1396.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>-11.1</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Euro Pratik Sales Limited</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>257.45</v>
+        <v>122.81</v>
       </c>
       <c r="J23" t="n">
-        <v>257.65</v>
+        <v>105.19</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1</v>
+        <v>16.8</v>
       </c>
       <c r="L23" t="n">
-        <v>70.09</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.062</v>
+        <v>0.053</v>
       </c>
       <c r="Q23" t="n">
-        <v>2631</v>
+        <v>4957</v>
       </c>
       <c r="R23" t="n">
-        <v>45.8</v>
+        <v>32.3</v>
       </c>
       <c r="S23" t="n">
-        <v>-3</v>
+        <v>-25</v>
       </c>
       <c r="T23" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>29.6</v>
+        <v>10.7</v>
       </c>
       <c r="X23" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="AA23" t="n">
-        <v>294.37</v>
+        <v>105.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>277.85</v>
+        <v>112.38</v>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I24" t="n">
-        <v>434.15</v>
+        <v>13.9</v>
       </c>
       <c r="J24" t="n">
-        <v>474.82</v>
+        <v>12.31</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.6</v>
+        <v>12.9</v>
       </c>
       <c r="L24" t="n">
-        <v>70.55</v>
+        <v>69.12</v>
       </c>
       <c r="M24" t="n">
-        <v>10.22</v>
+        <v>1.35</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.275</v>
+        <v>0.344</v>
       </c>
       <c r="Q24" t="n">
-        <v>3723</v>
+        <v>392</v>
       </c>
       <c r="R24" t="n">
-        <v>26</v>
+        <v>1265</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>127</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>-14</v>
+        <v>-98</v>
       </c>
       <c r="V24" t="n">
-        <v>6.41</v>
+        <v>0.01</v>
       </c>
       <c r="W24" t="n">
-        <v>9.890000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
-        <v>450.65</v>
+        <v>11.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>434.35</v>
+        <v>13.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.1</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>OBCL LIMITED (FORMERLY KNOWN AS ORISSA BENGAL CARRIER LIMITED)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
         <v>20</v>
       </c>
-      <c r="F25" t="n">
-        <v>14</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5</v>
-      </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I25" t="n">
-        <v>175.95</v>
+        <v>55.4</v>
       </c>
       <c r="J25" t="n">
-        <v>173.91</v>
+        <v>53.44</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>65.64</v>
+        <v>67.23</v>
       </c>
       <c r="M25" t="n">
-        <v>2.61</v>
+        <v>1.88</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.134</v>
+        <v>1.607</v>
       </c>
       <c r="Q25" t="n">
-        <v>1953</v>
-      </c>
-      <c r="R25" t="n">
-        <v>20.7</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="T25" t="n">
-        <v>26</v>
+        <v>2.47</v>
       </c>
       <c r="U25" t="n">
-        <v>-4</v>
+        <v>-3779</v>
       </c>
       <c r="V25" t="n">
-        <v>2.36</v>
+        <v>-0.05</v>
       </c>
       <c r="W25" t="n">
-        <v>14.2</v>
+        <v>-1.26</v>
       </c>
       <c r="X25" t="n">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>183.98</v>
+        <v>54.27</v>
       </c>
       <c r="AB25" t="n">
-        <v>190.89</v>
+        <v>55.13</v>
       </c>
       <c r="AC25" t="n">
-        <v>-16.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
+        <v>322</v>
+      </c>
+      <c r="J26" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1084</v>
+      </c>
+      <c r="R26" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>12</v>
+      </c>
+      <c r="T26" t="n">
+        <v>29</v>
+      </c>
+      <c r="U26" t="n">
+        <v>20</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="W26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>333.76</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>349.79</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SILVERTUC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>47</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>17</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>178.22</v>
+      </c>
+      <c r="J27" t="n">
+        <v>180.98</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>74.59</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2260</v>
+      </c>
+      <c r="R27" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="n">
+        <v>17</v>
+      </c>
+      <c r="U27" t="n">
+        <v>83</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W27" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>192.38</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>557.0599999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-87.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MOTOGENFIN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>47</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>25</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>27</v>
+      </c>
+      <c r="J28" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N28" t="n">
+        <v>15</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1.276</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>105</v>
+      </c>
+      <c r="R28" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>26</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GANESHCP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>45</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F29" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>174.15</v>
+      </c>
+      <c r="J29" t="n">
+        <v>201.21</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="M29" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>704</v>
+      </c>
+      <c r="R29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>21</v>
+      </c>
+      <c r="U29" t="n">
+        <v>45</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>177.46</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>200.72</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OMPOWER</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Om Power Transmission Limited</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>44</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>19</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>175.31</v>
+      </c>
+      <c r="J30" t="n">
+        <v>182.69</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>600</v>
+      </c>
+      <c r="R30" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>61</v>
+      </c>
+      <c r="T30" t="n">
+        <v>15</v>
+      </c>
+      <c r="U30" t="n">
+        <v>82</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="W30" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>171.77</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PKTEA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>44</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>744.75</v>
+      </c>
+      <c r="J31" t="n">
+        <v>717.77</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>231</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-184</v>
+      </c>
+      <c r="V31" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>731.34</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>760.58</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>THOMASCOOK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>44</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F32" t="n">
+        <v>14</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>108.43</v>
+      </c>
+      <c r="J32" t="n">
+        <v>109.31</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="M32" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>11-06-2026</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5100</v>
+      </c>
+      <c r="R32" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>42</v>
+      </c>
+      <c r="U32" t="n">
+        <v>8</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W32" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Y32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ARSSBL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>44</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>17</v>
+      </c>
+      <c r="F33" t="n">
+        <v>27</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>509.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>545.03</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3214</v>
+      </c>
+      <c r="R33" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S33" t="n">
+        <v>17</v>
+      </c>
+      <c r="T33" t="n">
+        <v>97</v>
+      </c>
+      <c r="U33" t="n">
+        <v>53</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="W33" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Y33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>530.97</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>562.98</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GOKUL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>43</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="J34" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N34" t="n">
+        <v>22</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>420</v>
+      </c>
+      <c r="R34" t="n">
+        <v>104</v>
+      </c>
+      <c r="S34" t="n">
+        <v>246</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="U34" t="n">
+        <v>10</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AJMERA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>43</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>25</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>117.41</v>
+      </c>
+      <c r="J35" t="n">
+        <v>114.86</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>69.73999999999999</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>04-06-2026</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2311</v>
+      </c>
+      <c r="R35" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S35" t="n">
+        <v>18</v>
+      </c>
+      <c r="T35" t="n">
+        <v>46</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W35" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>327.83</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-12.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DOLLAR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>43</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>17</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>268.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1524</v>
+      </c>
+      <c r="R36" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>46</v>
+      </c>
+      <c r="U36" t="n">
+        <v>18</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="W36" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="Y36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>267.86</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>294.37</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VIVIANA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VIVIANA POWER TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>42</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>728.4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>815.16</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>737</v>
+      </c>
+      <c r="R37" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>185</v>
+      </c>
+      <c r="T37" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="U37" t="n">
+        <v>204</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="W37" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Y37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>750.1</v>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>-19.9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TRUALT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TRUALT BIOENERGY LIMITED</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>40</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>434.15</v>
+      </c>
+      <c r="J38" t="n">
+        <v>474.82</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="M38" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3723</v>
+      </c>
+      <c r="R38" t="n">
+        <v>26</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>127</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-14</v>
+      </c>
+      <c r="V38" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="W38" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>450.65</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>434.35</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EUROPRATIK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Euro Pratik Sales Limited</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>40</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>17</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>257.45</v>
+      </c>
+      <c r="J39" t="n">
+        <v>257.65</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2631</v>
+      </c>
+      <c r="R39" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>11</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>294.37</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>277.85</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HEXAGON</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HEXAGON NUTRITION LIMITED</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>39</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Fundamental Watch</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>15</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="J40" t="n">
+        <v>64.04000000000001</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L40" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>840</v>
+      </c>
+      <c r="R40" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Y40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>66.20999999999999</v>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LAOPALA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LA OPALA RG LIMITED</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Fundamental Watch</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>175.95</v>
+      </c>
+      <c r="J41" t="n">
+        <v>173.91</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>08-06-2026</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1953</v>
+      </c>
+      <c r="R41" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>26</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W41" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>183.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>190.89</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>-16.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BMWVENTLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BMW VENTURES LIMITED</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>38</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fundamental Watch</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" t="n">
+        <v>23</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="J42" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="L42" t="n">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>491</v>
+      </c>
+      <c r="R42" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>19</v>
+      </c>
+      <c r="T42" t="n">
+        <v>21</v>
+      </c>
+      <c r="U42" t="n">
+        <v>20</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W42" t="n">
+        <v>12</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Y42" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GRMOVER</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GRM OVERSEAS LIMITED</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>35</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fundamental Watch</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>25</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>86.38</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J43" t="n">
         <v>95.54000000000001</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K43" t="n">
         <v>-9.6</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L43" t="n">
         <v>71.72</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M43" t="n">
         <v>10.87</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N43" t="n">
         <v>6</v>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>24-06-2026</t>
         </is>
       </c>
-      <c r="P26" t="n">
+      <c r="P43" t="n">
         <v>0.607</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q43" t="n">
         <v>1790</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R43" t="n">
         <v>32.3</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S43" t="n">
         <v>39</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T43" t="n">
         <v>31</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U43" t="n">
         <v>8</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V43" t="n">
         <v>0.9</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W43" t="n">
         <v>11.3</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X43" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y26" t="b">
+      <c r="Y43" t="b">
         <v>0</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z43" t="n">
         <v>9</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AA43" t="n">
         <v>91.54000000000001</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AB43" t="n">
         <v>191.63</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AC43" t="n">
         <v>-45.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SRHHYPOLTD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>34</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Fundamental Watch</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" t="n">
+        <v>14</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>473.95</v>
+      </c>
+      <c r="J44" t="n">
+        <v>471.92</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>28-08-2026</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>814</v>
+      </c>
+      <c r="R44" t="n">
+        <v>8</v>
+      </c>
+      <c r="S44" t="n">
+        <v>7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>30</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="W44" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y44" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>488.96</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>489.03</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MBEL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M &amp; B Engineering Limited</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>32</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Fundamental Watch</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>20</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>271.35</v>
+      </c>
+      <c r="J45" t="n">
+        <v>292.28</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1551</v>
+      </c>
+      <c r="R45" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="n">
+        <v>21</v>
+      </c>
+      <c r="U45" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W45" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>298.79</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>325.09</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>-16.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TIGERLOGS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tiger Logistics (India) Limited</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fundamental Watch</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>20</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="L46" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N46" t="n">
+        <v>13</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>311</v>
+      </c>
+      <c r="R46" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>16</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-30</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="W46" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VSTL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>29</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>20</v>
+      </c>
+      <c r="F47" t="n">
+        <v>11</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>110.82</v>
+      </c>
+      <c r="J47" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N47" t="n">
+        <v>9</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>210</v>
+      </c>
+      <c r="R47" t="n">
+        <v>25</v>
+      </c>
+      <c r="S47" t="n">
+        <v>21</v>
+      </c>
+      <c r="T47" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="U47" t="n">
+        <v>-29</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W47" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Y47" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>120.22</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WCIL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>26</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>85.73999999999999</v>
+      </c>
+      <c r="J48" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="L48" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>874</v>
+      </c>
+      <c r="R48" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="S48" t="n">
+        <v>9</v>
+      </c>
+      <c r="T48" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="U48" t="n">
+        <v>-36</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="W48" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>104.38</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>-26.2</v>
       </c>
     </row>
   </sheetData>
@@ -3034,7 +5148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3168,238 +5282,238 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>MACPOWER CNC MACHINES LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5440.5</v>
+        <v>2007.1</v>
       </c>
       <c r="D4" t="n">
-        <v>5187.29</v>
+        <v>920.51</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
-        <v>67.16</v>
+        <v>73.16</v>
       </c>
       <c r="G4" t="n">
-        <v>6.71</v>
+        <v>0.44</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>813.45</v>
+        <v>238.75</v>
       </c>
       <c r="D5" t="n">
-        <v>745.6900000000001</v>
+        <v>217.8</v>
       </c>
       <c r="E5" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="F5" t="n">
-        <v>69.61</v>
+        <v>71.75</v>
       </c>
       <c r="G5" t="n">
-        <v>9.18</v>
+        <v>0.82</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>542.25</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>390.61</v>
+        <v>70.19</v>
       </c>
       <c r="E6" t="n">
-        <v>38.8</v>
+        <v>2.2</v>
       </c>
       <c r="F6" t="n">
-        <v>63.09</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>8.02</v>
+        <v>0.91</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>636.9</v>
+        <v>5440.5</v>
       </c>
       <c r="D7" t="n">
-        <v>567.47</v>
+        <v>5187.29</v>
       </c>
       <c r="E7" t="n">
-        <v>12.2</v>
+        <v>4.9</v>
       </c>
       <c r="F7" t="n">
-        <v>64.68000000000001</v>
+        <v>67.16</v>
       </c>
       <c r="G7" t="n">
-        <v>5.47</v>
+        <v>6.71</v>
       </c>
       <c r="H7" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>331.05</v>
+        <v>813.45</v>
       </c>
       <c r="D8" t="n">
-        <v>311.69</v>
+        <v>745.6900000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>6.2</v>
+        <v>9.1</v>
       </c>
       <c r="F8" t="n">
-        <v>63.24</v>
+        <v>69.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.41</v>
+        <v>9.18</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>81.51000000000001</v>
+        <v>542.25</v>
       </c>
       <c r="D9" t="n">
-        <v>74.92</v>
+        <v>390.61</v>
       </c>
       <c r="E9" t="n">
-        <v>8.800000000000001</v>
+        <v>38.8</v>
       </c>
       <c r="F9" t="n">
-        <v>62.78</v>
+        <v>63.09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.48</v>
+        <v>8.02</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100.04</v>
+        <v>267.49</v>
       </c>
       <c r="D10" t="n">
-        <v>89.34</v>
+        <v>243.52</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>70.88</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>6.25</v>
+        <v>1.11</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -3413,346 +5527,346 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>139.39</v>
+        <v>354.85</v>
       </c>
       <c r="D11" t="n">
-        <v>100.9</v>
+        <v>335.41</v>
       </c>
       <c r="E11" t="n">
-        <v>38.1</v>
+        <v>5.8</v>
       </c>
       <c r="F11" t="n">
-        <v>69.56</v>
+        <v>68.48</v>
       </c>
       <c r="G11" t="n">
-        <v>3.01</v>
+        <v>0.41</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1316.1</v>
+        <v>366.7</v>
       </c>
       <c r="D12" t="n">
-        <v>1104.34</v>
+        <v>338.1</v>
       </c>
       <c r="E12" t="n">
-        <v>19.2</v>
+        <v>8.5</v>
       </c>
       <c r="F12" t="n">
-        <v>60.82</v>
+        <v>66.73</v>
       </c>
       <c r="G12" t="n">
-        <v>5.22</v>
+        <v>0.34</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13.9</v>
+        <v>192.36</v>
       </c>
       <c r="D13" t="n">
-        <v>12.31</v>
+        <v>164.1</v>
       </c>
       <c r="E13" t="n">
-        <v>12.9</v>
+        <v>17.2</v>
       </c>
       <c r="F13" t="n">
-        <v>69.12</v>
+        <v>60.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.35</v>
+        <v>0.25</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>122.81</v>
+        <v>636.9</v>
       </c>
       <c r="D14" t="n">
-        <v>105.19</v>
+        <v>567.47</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8</v>
+        <v>12.2</v>
       </c>
       <c r="F14" t="n">
-        <v>67.15000000000001</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>2.63</v>
+        <v>5.47</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OBCL LIMITED (FORMERLY KNOWN AS ORISSA BENGAL CARRIER LIMITED)</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.4</v>
+        <v>331.05</v>
       </c>
       <c r="D15" t="n">
-        <v>53.44</v>
+        <v>311.69</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="F15" t="n">
-        <v>67.23</v>
+        <v>63.24</v>
       </c>
       <c r="G15" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="H15" t="n">
         <v>7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>322</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>297.3</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>8.300000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="F16" t="n">
-        <v>67.69</v>
+        <v>72.53</v>
       </c>
       <c r="G16" t="n">
-        <v>2.97</v>
+        <v>0.42</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>19.86</v>
       </c>
       <c r="D17" t="n">
-        <v>29.14</v>
+        <v>21.01</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.3</v>
+        <v>-5.5</v>
       </c>
       <c r="F17" t="n">
-        <v>69.03</v>
+        <v>70.87</v>
       </c>
       <c r="G17" t="n">
-        <v>1.34</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>174.15</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>201.21</v>
+        <v>76.98</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.4</v>
+        <v>5.9</v>
       </c>
       <c r="F18" t="n">
-        <v>64.08</v>
+        <v>62.78</v>
       </c>
       <c r="G18" t="n">
-        <v>8.07</v>
+        <v>2.64</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>744.75</v>
+        <v>100.04</v>
       </c>
       <c r="D19" t="n">
-        <v>717.77</v>
+        <v>89.34</v>
       </c>
       <c r="E19" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>61.71</v>
+        <v>70.88</v>
       </c>
       <c r="G19" t="n">
-        <v>1.61</v>
+        <v>6.25</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>108.43</v>
+        <v>139.39</v>
       </c>
       <c r="D20" t="n">
-        <v>109.31</v>
+        <v>100.9</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8</v>
+        <v>38.1</v>
       </c>
       <c r="F20" t="n">
-        <v>72.34</v>
+        <v>69.56</v>
       </c>
       <c r="G20" t="n">
-        <v>48.4</v>
+        <v>3.01</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3763,210 +5877,980 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AJMERA</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>117.41</v>
+        <v>213</v>
       </c>
       <c r="D21" t="n">
-        <v>114.86</v>
+        <v>209.98</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="F21" t="n">
-        <v>69.73999999999999</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>7.36</v>
+        <v>0.26</v>
       </c>
       <c r="H21" t="n">
         <v>4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>268.7</v>
+        <v>1316.1</v>
       </c>
       <c r="D22" t="n">
-        <v>269.7</v>
+        <v>1104.34</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4</v>
+        <v>19.2</v>
       </c>
       <c r="F22" t="n">
-        <v>73.09</v>
+        <v>60.82</v>
       </c>
       <c r="G22" t="n">
-        <v>1.48</v>
+        <v>5.22</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Euro Pratik Sales Limited</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>257.45</v>
+        <v>122.81</v>
       </c>
       <c r="D23" t="n">
-        <v>257.65</v>
+        <v>105.19</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1</v>
+        <v>16.8</v>
       </c>
       <c r="F23" t="n">
-        <v>70.09</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>434.15</v>
+        <v>13.9</v>
       </c>
       <c r="D24" t="n">
-        <v>474.82</v>
+        <v>12.31</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.6</v>
+        <v>12.9</v>
       </c>
       <c r="F24" t="n">
-        <v>70.55</v>
+        <v>69.12</v>
       </c>
       <c r="G24" t="n">
-        <v>10.22</v>
+        <v>1.35</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>OBCL LIMITED (FORMERLY KNOWN AS ORISSA BENGAL CARRIER LIMITED)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>175.95</v>
+        <v>55.4</v>
       </c>
       <c r="D25" t="n">
-        <v>173.91</v>
+        <v>53.44</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="F25" t="n">
-        <v>65.64</v>
+        <v>67.23</v>
       </c>
       <c r="G25" t="n">
-        <v>2.61</v>
+        <v>1.88</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>BAJAJHCARE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>322</v>
+      </c>
+      <c r="D26" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F26" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SILVERTUC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>178.22</v>
+      </c>
+      <c r="D27" t="n">
+        <v>180.98</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>74.59</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MOTOGENFIN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GANESHCP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>174.15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>201.21</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OMPOWER</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Om Power Transmission Limited</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>175.31</v>
+      </c>
+      <c r="D30" t="n">
+        <v>182.69</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PKTEA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>744.75</v>
+      </c>
+      <c r="D31" t="n">
+        <v>717.77</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>THOMASCOOK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>108.43</v>
+      </c>
+      <c r="D32" t="n">
+        <v>109.31</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="G32" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ARSSBL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>509.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>545.03</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GOKUL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="D34" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H34" t="n">
+        <v>22</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AJMERA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>117.41</v>
+      </c>
+      <c r="D35" t="n">
+        <v>114.86</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>69.73999999999999</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>04-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DOLLAR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>268.7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VIVIANA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VIVIANA POWER TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>728.4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>815.16</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TRUALT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TRUALT BIOENERGY LIMITED</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>434.15</v>
+      </c>
+      <c r="D38" t="n">
+        <v>474.82</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="G38" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EUROPRATIK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Euro Pratik Sales Limited</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>257.45</v>
+      </c>
+      <c r="D39" t="n">
+        <v>257.65</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HEXAGON</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HEXAGON NUTRITION LIMITED</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="D40" t="n">
+        <v>64.04000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LAOPALA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LA OPALA RG LIMITED</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>175.95</v>
+      </c>
+      <c r="D41" t="n">
+        <v>173.91</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>08-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BMWVENTLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BMW VENTURES LIMITED</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="D42" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>GRMOVER</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C43" t="n">
         <v>86.38</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D43" t="n">
         <v>95.54000000000001</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E43" t="n">
         <v>-9.6</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F43" t="n">
         <v>71.72</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G43" t="n">
         <v>10.87</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H43" t="n">
         <v>6</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>24-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SRHHYPOLTD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>473.95</v>
+      </c>
+      <c r="D44" t="n">
+        <v>471.92</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>28-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MBEL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M &amp; B Engineering Limited</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>271.35</v>
+      </c>
+      <c r="D45" t="n">
+        <v>292.28</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TIGERLOGS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tiger Logistics (India) Limited</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="D46" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="F46" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H46" t="n">
+        <v>13</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VSTL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>110.82</v>
+      </c>
+      <c r="D47" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H47" t="n">
+        <v>9</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WCIL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>85.73999999999999</v>
+      </c>
+      <c r="D48" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
         </is>
       </c>
     </row>
@@ -3981,7 +6865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4003,7 +6887,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -4013,7 +6897,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -4033,7 +6917,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -4043,47 +6927,57 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[Category] Buy on Breakout</t>
+          <t>[Category] Avoid</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[Category] Fundamental Watch</t>
+          <t>[Category] Buy on Breakout</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[Category] Strong Buy Setup</t>
+          <t>[Category] Fundamental Watch</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>[Category] Strong Buy Setup</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>[Category] Watchlist</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>10</v>
+      <c r="B11" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/2026-08-28/enriched_analysis.xlsx
+++ b/output/2026-08-28/enriched_analysis.xlsx
@@ -1900,27 +1900,27 @@
         <v>331.05</v>
       </c>
       <c r="J15" t="n">
-        <v>311.69</v>
+        <v>314.32</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
         <v>63.24</v>
       </c>
       <c r="M15" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.446</v>
+        <v>0.551</v>
       </c>
       <c r="Q15" t="n">
         <v>316</v>
@@ -5679,23 +5679,23 @@
         <v>331.05</v>
       </c>
       <c r="D15" t="n">
-        <v>311.69</v>
+        <v>314.32</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="F15" t="n">
         <v>63.24</v>
       </c>
       <c r="G15" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
